--- a/Preços P7.xlsx
+++ b/Preços P7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matil\Desktop\menu-posto-7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D14B2B-7140-45A5-B853-E3EEE5329E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40105C7-4540-48F5-805A-86E54177DCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1165,7 +1165,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,22 +1176,26 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1200,6 +1204,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1222,7 +1233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1252,6 +1263,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1525,7 +1539,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>10</v>
@@ -1547,7 +1561,7 @@
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="11">
         <v>2</v>
       </c>
       <c r="F4" s="5" t="s">

--- a/Preços P7.xlsx
+++ b/Preços P7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matil\Desktop\menu-posto-7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40105C7-4540-48F5-805A-86E54177DCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0FD685-1A12-4B62-B41A-7BC0A38AA4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1165,7 +1165,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1205,13 +1205,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1233,7 +1226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1263,9 +1256,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1539,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>10</v>
@@ -1561,7 +1551,7 @@
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="4">
         <v>2</v>
       </c>
       <c r="F4" s="5" t="s">

--- a/Preços P7.xlsx
+++ b/Preços P7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matil\Desktop\menu-posto-7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0FD685-1A12-4B62-B41A-7BC0A38AA4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09D57D0-E700-4603-B3C3-6B61940E81D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="386">
   <si>
     <t>Secção</t>
   </si>
@@ -66,12 +66,6 @@
     <t>Café / Descafeinado</t>
   </si>
   <si>
-    <t>Café duplo</t>
-  </si>
-  <si>
-    <t>Double expresso</t>
-  </si>
-  <si>
     <t>Double Café</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Meia de Leite</t>
   </si>
   <si>
-    <t>Espresso with milk</t>
-  </si>
-  <si>
     <t>Café au Lait</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>Garoto</t>
   </si>
   <si>
-    <t>Small coffee with milk (Garoto)</t>
-  </si>
-  <si>
     <t>Petit Café au Lait</t>
   </si>
   <si>
@@ -105,9 +93,6 @@
     <t>Galão</t>
   </si>
   <si>
-    <t>Latte/ coffee with milk (Galão)</t>
-  </si>
-  <si>
     <t>Grand Café au Lait</t>
   </si>
   <si>
@@ -126,15 +111,6 @@
     <t>Té / Infusión</t>
   </si>
   <si>
-    <t>Carioca de café/limão</t>
-  </si>
-  <si>
-    <t>Mild coffee/ lemon</t>
-  </si>
-  <si>
-    <t>Café allongé / infusion de citron</t>
-  </si>
-  <si>
     <t>Café Suave / Infusión de Limón</t>
   </si>
   <si>
@@ -153,36 +129,18 @@
     <t>Agua Mineral 0,33 L</t>
   </si>
   <si>
-    <t>Água tónica</t>
-  </si>
-  <si>
-    <t>Tonic water</t>
-  </si>
-  <si>
     <t>Eau Tonique</t>
   </si>
   <si>
     <t>Agua Tónica</t>
   </si>
   <si>
-    <t>Água com gás</t>
-  </si>
-  <si>
-    <t>Sparkling water</t>
-  </si>
-  <si>
     <t>Eau Gazeuse</t>
   </si>
   <si>
     <t>Agua con Gas</t>
   </si>
   <si>
-    <t>Água sabores</t>
-  </si>
-  <si>
-    <t>Flavoured water</t>
-  </si>
-  <si>
     <t>Eau Aromatisée</t>
   </si>
   <si>
@@ -201,9 +159,6 @@
     <t>Fanta</t>
   </si>
   <si>
-    <t>Red bull</t>
-  </si>
-  <si>
     <t>Compal</t>
   </si>
   <si>
@@ -342,9 +297,6 @@
     <t>Somersby 0,5L</t>
   </si>
   <si>
-    <t>Somersby jarra</t>
-  </si>
-  <si>
     <t>Somersby Pitcher</t>
   </si>
   <si>
@@ -381,18 +333,12 @@
     <t>Favaios</t>
   </si>
   <si>
-    <t>Favaios &amp; fino</t>
-  </si>
-  <si>
     <t>Favaios &amp; Draft Beer</t>
   </si>
   <si>
     <t>Favaios &amp; Bièrre Pression</t>
   </si>
   <si>
-    <t>Favaios &amp; Caña pequeña</t>
-  </si>
-  <si>
     <t>Martini</t>
   </si>
   <si>
@@ -480,9 +426,6 @@
     <t>Jagermeister</t>
   </si>
   <si>
-    <t>Licor de café</t>
-  </si>
-  <si>
     <t>Limoncello</t>
   </si>
   <si>
@@ -522,9 +465,6 @@
     <t>Sangria (Glass)</t>
   </si>
   <si>
-    <t>Sangria (verre)</t>
-  </si>
-  <si>
     <t>Sangría (Copa)</t>
   </si>
   <si>
@@ -546,9 +486,6 @@
     <t>Vino (Copa)</t>
   </si>
   <si>
-    <t>Vinho garrafa</t>
-  </si>
-  <si>
     <t>Wine (Bottle)</t>
   </si>
   <si>
@@ -567,21 +504,9 @@
     <t>Vin Mousseux</t>
   </si>
   <si>
-    <t>Vino Espumoso (Cava)</t>
-  </si>
-  <si>
-    <t>Sangria espumante</t>
-  </si>
-  <si>
     <t>Sparkling Wine Sangria</t>
   </si>
   <si>
-    <t>Sangria au mousseux</t>
-  </si>
-  <si>
-    <t>Sangría de Cava</t>
-  </si>
-  <si>
     <t>ESPIRITUOSAS</t>
   </si>
   <si>
@@ -804,9 +729,6 @@
     <t>Tequila casa</t>
   </si>
   <si>
-    <t>House tequila</t>
-  </si>
-  <si>
     <t>Tequila Maison</t>
   </si>
   <si>
@@ -816,9 +738,6 @@
     <t>Vodka casa</t>
   </si>
   <si>
-    <t>Houve vodka</t>
-  </si>
-  <si>
     <t>Vodka Maison</t>
   </si>
   <si>
@@ -1005,9 +924,6 @@
     <t>Asinhas</t>
   </si>
   <si>
-    <t>Chicken wings</t>
-  </si>
-  <si>
     <t>Ailes de Poulet</t>
   </si>
   <si>
@@ -1029,9 +945,6 @@
     <t>Coxinhas</t>
   </si>
   <si>
-    <t>Brazilian Chicken croquetes</t>
-  </si>
-  <si>
     <t>Coxinhas (Croquettes de Poulet)</t>
   </si>
   <si>
@@ -1059,9 +972,6 @@
     <t>Mini Rissóis</t>
   </si>
   <si>
-    <t>Mini rissóis/ pastry croquetes</t>
-  </si>
-  <si>
     <t>Mini Friands</t>
   </si>
   <si>
@@ -1074,21 +984,12 @@
     <t>Pastéis de Bacalhau</t>
   </si>
   <si>
-    <t>Codfish cakes</t>
-  </si>
-  <si>
     <t>Beignets de Morue</t>
   </si>
   <si>
-    <t>Buñuelos de bacalao</t>
-  </si>
-  <si>
     <t>Sticks de Mozzarela</t>
   </si>
   <si>
-    <t>Mozzarela sticks</t>
-  </si>
-  <si>
     <t>Bâtonnets de Mozzarella</t>
   </si>
   <si>
@@ -1098,9 +999,6 @@
     <t>Tabua de frios</t>
   </si>
   <si>
-    <t>Cold cuts and cheese board</t>
-  </si>
-  <si>
     <t>Planche de Charcuterie et Fromages</t>
   </si>
   <si>
@@ -1116,9 +1014,6 @@
     <t>Planche Signature P7</t>
   </si>
   <si>
-    <t>Tabla P7 (Especial de la Casa</t>
-  </si>
-  <si>
     <t>Tira Gosto</t>
   </si>
   <si>
@@ -1146,9 +1041,6 @@
     <t>Tremoços</t>
   </si>
   <si>
-    <t>Lupin beans</t>
-  </si>
-  <si>
     <t>Grained de Lupins</t>
   </si>
   <si>
@@ -1156,6 +1048,141 @@
   </si>
   <si>
     <t>Empalhada</t>
+  </si>
+  <si>
+    <t>Café Duplo</t>
+  </si>
+  <si>
+    <t>Água Tónica</t>
+  </si>
+  <si>
+    <t>Água Sabores</t>
+  </si>
+  <si>
+    <t>Carioca de Café / Limão</t>
+  </si>
+  <si>
+    <t>Água com Gás</t>
+  </si>
+  <si>
+    <t>Somersby Jarra</t>
+  </si>
+  <si>
+    <t>Godfather</t>
+  </si>
+  <si>
+    <t>Red Bull</t>
+  </si>
+  <si>
+    <t>Favaios &amp; Fino</t>
+  </si>
+  <si>
+    <t>Sangria Espumante</t>
+  </si>
+  <si>
+    <t>Sangria au Mousseux</t>
+  </si>
+  <si>
+    <t>Vinho (Garrafa)</t>
+  </si>
+  <si>
+    <t>Vino Espumoso</t>
+  </si>
+  <si>
+    <t>Sangría de Vino Espumoso</t>
+  </si>
+  <si>
+    <t>Dewar's 12 years</t>
+  </si>
+  <si>
+    <t>Dewar's 12 ans</t>
+  </si>
+  <si>
+    <t>Dewar's 12 años</t>
+  </si>
+  <si>
+    <t>Dewar's 15 years</t>
+  </si>
+  <si>
+    <t>Dewar's 15 ans</t>
+  </si>
+  <si>
+    <t>Dewar's 15 años</t>
+  </si>
+  <si>
+    <t>House Tequila</t>
+  </si>
+  <si>
+    <t>Houve Vodka</t>
+  </si>
+  <si>
+    <t>Chicken Wings</t>
+  </si>
+  <si>
+    <t>Brazilian Chicken Croquetes</t>
+  </si>
+  <si>
+    <t>Mini Croquetes</t>
+  </si>
+  <si>
+    <t>Mini Rissóis/ Pastry Croquetes</t>
+  </si>
+  <si>
+    <t>Codfish Cakes</t>
+  </si>
+  <si>
+    <t>Mozzarela Sticks</t>
+  </si>
+  <si>
+    <t>Cold Cuts and Cheese Board</t>
+  </si>
+  <si>
+    <t>Lupin Beans</t>
+  </si>
+  <si>
+    <t>Café Allongé / Infusion de Citron</t>
+  </si>
+  <si>
+    <t>Sangria (Verre)</t>
+  </si>
+  <si>
+    <t>Licor de Café</t>
+  </si>
+  <si>
+    <t>Havana Spécial</t>
+  </si>
+  <si>
+    <t>Double Expresso</t>
+  </si>
+  <si>
+    <t>Espresso with Milk</t>
+  </si>
+  <si>
+    <t>Small Coffee with Milk (Garoto)</t>
+  </si>
+  <si>
+    <t>Latte / Coffee with Milk (Galão)</t>
+  </si>
+  <si>
+    <t>Mild Coffee / Lemon</t>
+  </si>
+  <si>
+    <t>Tonic Water</t>
+  </si>
+  <si>
+    <t>Sparkling Water</t>
+  </si>
+  <si>
+    <t>Flavoured Water</t>
+  </si>
+  <si>
+    <t>Favaios &amp; Caña Pequeña</t>
+  </si>
+  <si>
+    <t>Buñuelos de Bacalao</t>
+  </si>
+  <si>
+    <t>Tabla P7 (Especial de la Casa)</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1183,12 +1210,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
@@ -1226,7 +1247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1240,22 +1261,16 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1474,19 +1489,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H1001"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10"/>
+      <c r="A1" s="8"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1525,19 +1540,19 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>1</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1548,20 +1563,20 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
+      <c r="D4" s="6" t="s">
+        <v>341</v>
       </c>
       <c r="E4" s="4">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1571,20 +1586,20 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>17</v>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="E5" s="4">
         <v>1.5</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>20</v>
+      <c r="F5" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1594,20 +1609,20 @@
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>24</v>
+      <c r="F6" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1617,20 +1632,20 @@
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E7" s="4">
         <v>1.5</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>28</v>
+      <c r="F7" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1640,20 +1655,20 @@
       <c r="C8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>29</v>
+      <c r="D8" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="E8" s="4">
         <v>1.5</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>32</v>
+      <c r="F8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1663,20 +1678,20 @@
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
+      <c r="D9" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>36</v>
+      <c r="F9" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1684,22 +1699,22 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="E10" s="4">
         <v>1</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>41</v>
+      <c r="F10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1707,22 +1722,22 @@
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>45</v>
+      <c r="F11" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -1730,22 +1745,22 @@
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>49</v>
+      <c r="F12" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1753,22 +1768,22 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>53</v>
+      <c r="F13" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1776,22 +1791,22 @@
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E14" s="4">
         <v>2.5</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1799,22 +1814,22 @@
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E15" s="4">
         <v>2.5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1822,22 +1837,22 @@
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E16" s="4">
         <v>2.5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
@@ -1845,22 +1860,22 @@
         <v>7</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="E17" s="4">
         <v>3.5</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
@@ -1868,22 +1883,22 @@
         <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
@@ -1891,22 +1906,22 @@
         <v>7</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
@@ -1914,22 +1929,22 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
@@ -1937,22 +1952,22 @@
         <v>7</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E21" s="4">
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
@@ -1960,22 +1975,22 @@
         <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>66</v>
+        <v>40</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="E22" s="4">
         <v>1.5</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>69</v>
+      <c r="F22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
@@ -1983,22 +1998,22 @@
         <v>7</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>71</v>
+        <v>55</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E23" s="4">
         <v>1.6</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>74</v>
+      <c r="F23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -2006,22 +2021,22 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="E24" s="4">
         <v>2.5</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>78</v>
+      <c r="F24" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
@@ -2029,22 +2044,22 @@
         <v>7</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>79</v>
+        <v>55</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="E25" s="4">
         <v>2.5</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>82</v>
+      <c r="F25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
@@ -2052,22 +2067,22 @@
         <v>7</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>86</v>
+      <c r="F26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
@@ -2075,22 +2090,22 @@
         <v>7</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>87</v>
+        <v>55</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>90</v>
+      <c r="F27" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
@@ -2098,22 +2113,22 @@
         <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>91</v>
+        <v>55</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E28" s="4">
         <v>3</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>94</v>
+      <c r="F28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
@@ -2121,22 +2136,22 @@
         <v>7</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>95</v>
+        <v>55</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="E29" s="4">
         <v>3</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>98</v>
+      <c r="F29" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
@@ -2144,22 +2159,22 @@
         <v>7</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>99</v>
+        <v>55</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="E30" s="4">
         <v>4</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>102</v>
+      <c r="F30" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -2167,22 +2182,22 @@
         <v>7</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E31" s="4">
         <v>3.5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
@@ -2190,22 +2205,22 @@
         <v>7</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>104</v>
+        <v>55</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E32" s="4">
         <v>5</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>104</v>
+      <c r="F32" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
@@ -2213,22 +2228,22 @@
         <v>7</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>105</v>
+        <v>55</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>346</v>
       </c>
       <c r="E33" s="4">
         <v>10</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>108</v>
+      <c r="F33" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
@@ -2236,22 +2251,22 @@
         <v>7</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E34" s="4">
         <v>2.5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -2259,22 +2274,22 @@
         <v>7</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E35" s="4">
         <v>3</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
@@ -2282,22 +2297,22 @@
         <v>7</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E36" s="4">
         <v>3</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
@@ -2305,22 +2320,22 @@
         <v>7</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E37" s="4">
         <v>2.5</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
@@ -2328,22 +2343,22 @@
         <v>7</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E38" s="4">
         <v>1.5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
@@ -2351,22 +2366,22 @@
         <v>7</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E39" s="4">
         <v>3</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
@@ -2374,22 +2389,22 @@
         <v>7</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E40" s="4">
         <v>3</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
@@ -2397,22 +2412,22 @@
         <v>7</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E41" s="4">
         <v>3</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
@@ -2420,22 +2435,22 @@
         <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>118</v>
+        <v>349</v>
       </c>
       <c r="E42" s="4">
         <v>3.5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>121</v>
+        <v>383</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
@@ -2443,22 +2458,22 @@
         <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E43" s="4">
         <v>3</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
@@ -2466,22 +2481,22 @@
         <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E44" s="4">
         <v>3.5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
@@ -2489,22 +2504,22 @@
         <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E45" s="4">
         <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
@@ -2512,22 +2527,22 @@
         <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E46" s="4">
         <v>7.5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
@@ -2535,22 +2550,22 @@
         <v>7</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E47" s="4">
         <v>3</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
@@ -2558,22 +2573,22 @@
         <v>7</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E48" s="4">
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
@@ -2581,22 +2596,22 @@
         <v>7</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E49" s="4">
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
@@ -2604,22 +2619,22 @@
         <v>7</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E50" s="4">
         <v>3</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
@@ -2627,22 +2642,22 @@
         <v>7</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="E51" s="4">
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
@@ -2650,22 +2665,22 @@
         <v>7</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E52" s="4">
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
@@ -2673,22 +2688,22 @@
         <v>7</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="E53" s="4">
         <v>3</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
@@ -2696,22 +2711,22 @@
         <v>7</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E54" s="4">
         <v>4.5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
@@ -2719,22 +2734,22 @@
         <v>7</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="E55" s="4">
         <v>7.5</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
@@ -2742,22 +2757,22 @@
         <v>7</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E56" s="4">
         <v>7.5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.3">
@@ -2765,22 +2780,22 @@
         <v>7</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="E57" s="4">
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
@@ -2788,22 +2803,22 @@
         <v>7</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="E58" s="4">
         <v>7.5</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
@@ -2811,22 +2826,22 @@
         <v>7</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>151</v>
+        <v>373</v>
       </c>
       <c r="E59" s="4">
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>151</v>
+        <v>373</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>151</v>
+        <v>373</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>151</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
@@ -2834,22 +2849,22 @@
         <v>7</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E60" s="4">
         <v>7.5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
@@ -2857,22 +2872,22 @@
         <v>7</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
@@ -2880,22 +2895,22 @@
         <v>7</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="E62" s="4">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
@@ -2903,22 +2918,22 @@
         <v>7</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E63" s="4">
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
@@ -2926,22 +2941,22 @@
         <v>7</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
@@ -2949,22 +2964,22 @@
         <v>7</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="E65" s="4">
         <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
@@ -2972,22 +2987,22 @@
         <v>7</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E66" s="4">
         <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
@@ -2995,22 +3010,22 @@
         <v>7</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E67" s="4">
         <v>7.5</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
@@ -3018,22 +3033,22 @@
         <v>7</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E68" s="4">
         <v>10</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
@@ -3041,22 +3056,22 @@
         <v>7</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>163</v>
+        <v>143</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="E69" s="4">
         <v>4</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>166</v>
+      <c r="F69" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.3">
@@ -3064,22 +3079,22 @@
         <v>7</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>167</v>
+        <v>143</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="E70" s="4">
         <v>15</v>
       </c>
-      <c r="F70" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>168</v>
+      <c r="F70" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.3">
@@ -3087,22 +3102,22 @@
         <v>7</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>169</v>
+        <v>143</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="E71" s="4">
         <v>3</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>172</v>
+      <c r="F71" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
@@ -3110,22 +3125,22 @@
         <v>7</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>173</v>
+        <v>143</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>352</v>
       </c>
       <c r="E72" s="4">
         <v>12</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>176</v>
+      <c r="F72" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
@@ -3133,22 +3148,22 @@
         <v>7</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>177</v>
+        <v>143</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="E73" s="4">
         <v>20</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>180</v>
+      <c r="F73" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
@@ -3156,2654 +3171,2668 @@
         <v>7</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>181</v>
+        <v>143</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="E74" s="4">
         <v>18</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>184</v>
+      <c r="F74" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E75" s="4">
         <v>7.5</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="E76" s="4">
         <v>7.5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="E77" s="4">
         <v>7.5</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E78" s="4">
         <v>10</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="E79" s="4">
         <v>12.5</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="E80" s="4">
         <v>7.5</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="E81" s="4">
         <v>10</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="E82" s="4">
         <v>12</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="E83" s="4">
         <v>12.5</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="E84" s="4">
         <v>7.5</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="E85" s="4">
         <v>12.5</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="E86" s="4">
         <v>7.5</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E87" s="4">
         <v>10</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="E88" s="4">
         <v>12.5</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="E89" s="4">
         <v>7.5</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="E90" s="4">
         <v>7.5</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="E91" s="4">
         <v>6</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="E92" s="4">
         <v>7.5</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="E93" s="4">
         <v>7.5</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="E94" s="4">
         <v>12.5</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="E95" s="4">
         <v>6</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="E96" s="4">
         <v>10</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>217</v>
+        <v>374</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="E98" s="4">
         <v>12.5</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B99" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="E99" s="4">
         <v>12.5</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="E100" s="4">
         <v>7.5</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="E101" s="4">
         <v>10</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B102" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="E102" s="4">
         <v>20</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E103" s="4">
         <v>6</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="E104" s="4">
         <v>3</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="E105" s="4">
         <v>7.5</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="E106" s="4">
         <v>12.5</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B107" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="E107" s="4">
         <v>6</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B108" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="E108" s="4">
         <v>7.5</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B109" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E109" s="4">
         <v>7.5</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B110" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>233</v>
+        <v>355</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>233</v>
+        <v>356</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>233</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B111" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E111" s="4">
         <v>10</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B112" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="E112" s="4">
         <v>7.5</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B113" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E113" s="4">
         <v>7.5</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B114" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="E114" s="4">
         <v>7.5</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B115" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="E115" s="4">
         <v>10</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B116" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="E116" s="4">
         <v>12.5</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B117" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="E117" s="4">
         <v>10</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
     </row>
     <row r="118" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="E118" s="4">
         <v>10</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>242</v>
+        <v>358</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>242</v>
+        <v>359</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>242</v>
+        <v>360</v>
       </c>
     </row>
     <row r="119" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="E119" s="4">
         <v>10</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
     </row>
     <row r="120" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="E120" s="4">
         <v>10</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="E121" s="4">
         <v>10</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="E122" s="4">
         <v>10</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
     </row>
     <row r="123" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B123" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="E123" s="4">
         <v>9</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B124" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="E124" s="4">
         <v>10</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B125" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E125" s="4">
         <v>7.5</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
     </row>
     <row r="126" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B126" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="E126" s="4">
         <v>12.5</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
     </row>
     <row r="127" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B127" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="E127" s="4">
         <v>2.5</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
     </row>
     <row r="128" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B128" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="E128" s="4">
         <v>2.5</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
     </row>
     <row r="129" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B129" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>256</v>
+        <v>227</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="E129" s="4">
         <v>3</v>
       </c>
-      <c r="F129" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>256</v>
+      <c r="F129" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="130" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B130" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>257</v>
+        <v>227</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="E130" s="4">
         <v>3.5</v>
       </c>
-      <c r="F130" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>257</v>
+      <c r="F130" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="131" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B131" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>258</v>
+        <v>227</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>233</v>
       </c>
       <c r="E131" s="4">
         <v>2.5</v>
       </c>
-      <c r="F131" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>261</v>
+      <c r="F131" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B132" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>262</v>
+        <v>227</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>236</v>
       </c>
       <c r="E132" s="4">
         <v>2.5</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>265</v>
+      <c r="F132" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B133" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="E133" s="4">
         <v>5</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B134" s="3" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="E134" s="4">
         <v>5</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B135" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="E135" s="4">
         <v>7</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="136" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B136" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="E136" s="4">
         <v>7.5</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B137" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="E137" s="4">
         <v>7.5</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B138" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="E138" s="4">
         <v>7.5</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
     </row>
     <row r="139" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B139" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="E139" s="4">
         <v>10</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
     </row>
     <row r="140" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B140" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E140" s="4">
-        <v>10</v>
+        <v>347</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
     </row>
     <row r="141" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B141" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="E141" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B142" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="E142" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="143" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B143" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="E143" s="4">
         <v>10</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="144" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B144" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="E144" s="4">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B145" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="E145" s="4">
         <v>7.5</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B146" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="E146" s="4">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
     </row>
     <row r="147" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B147" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>283</v>
+        <v>254</v>
+      </c>
+      <c r="E147" s="4">
+        <v>10</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
     </row>
     <row r="148" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B148" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E148" s="4">
-        <v>10</v>
+        <v>255</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>256</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
     </row>
     <row r="149" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B149" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="E149" s="4">
         <v>10</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B150" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="E150" s="4">
         <v>10</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
     </row>
     <row r="151" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B151" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="E151" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
     </row>
     <row r="152" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B152" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="E152" s="4">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
     </row>
     <row r="153" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B153" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="E153" s="4">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
     </row>
     <row r="154" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B154" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E154" s="4">
         <v>10</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B155" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="E155" s="4">
         <v>10</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B156" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="E156" s="4">
         <v>10</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B157" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="E157" s="4">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="158" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B158" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="E158" s="4">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
     </row>
     <row r="159" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B159" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="E159" s="4">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B160" s="3" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="E160" s="4">
         <v>7.5</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
     </row>
     <row r="161" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B161" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="E161" s="4">
         <v>7.5</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B162" s="3" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="E162" s="4">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B163" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="E163" s="4">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B164" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="E164" s="4">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
     </row>
     <row r="165" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B165" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="E165" s="4">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
     </row>
     <row r="166" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B166" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="E166" s="4">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B167" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="E167" s="4">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B168" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="E168" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B169" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="E169" s="4">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
     </row>
     <row r="170" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B170" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="E170" s="4">
-        <v>4</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H170" s="7" t="s">
-        <v>311</v>
+        <v>1.5</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="171" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B171" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>312</v>
+        <v>280</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>281</v>
       </c>
       <c r="E171" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G171" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="H171" s="7" t="s">
-        <v>315</v>
+        <v>4</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H171" s="6" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="172" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B172" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>316</v>
+        <v>280</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>285</v>
       </c>
       <c r="E172" s="4">
         <v>4.5</v>
       </c>
-      <c r="F172" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>319</v>
+      <c r="F172" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="173" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B173" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>320</v>
+        <v>280</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="E173" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="H173" s="7" t="s">
-        <v>323</v>
+        <v>4.5</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H173" s="6" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="174" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B174" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>325</v>
+        <v>280</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>293</v>
       </c>
       <c r="E174" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>328</v>
+        <v>3.5</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="175" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B175" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C175" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>329</v>
+      <c r="D175" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="E175" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>332</v>
+        <v>4.5</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="176" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B176" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C176" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D176" s="5" t="s">
-        <v>333</v>
+      <c r="D176" s="6" t="s">
+        <v>301</v>
       </c>
       <c r="E176" s="4">
-        <v>4</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H176" s="7" t="s">
-        <v>336</v>
+        <v>2.5</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="177" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B177" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C177" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C177" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>337</v>
+      <c r="D177" s="6" t="s">
+        <v>305</v>
       </c>
       <c r="E177" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H177" s="7" t="s">
-        <v>338</v>
+        <v>4</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="178" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B178" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C178" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>340</v>
+      <c r="D178" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="E178" s="4">
         <v>3.5</v>
       </c>
-      <c r="F178" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="H178" s="7" t="s">
-        <v>342</v>
+      <c r="F178" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="179" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B179" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C179" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>343</v>
+      <c r="D179" s="6" t="s">
+        <v>311</v>
       </c>
       <c r="E179" s="4">
         <v>3.5</v>
       </c>
-      <c r="F179" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="G179" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="H179" s="7" t="s">
-        <v>346</v>
+      <c r="F179" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="180" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B180" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C180" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D180" s="5" t="s">
-        <v>347</v>
+      <c r="D180" s="6" t="s">
+        <v>314</v>
       </c>
       <c r="E180" s="4">
-        <v>4</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="H180" s="5" t="s">
-        <v>347</v>
+        <v>3.5</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="181" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B181" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C181" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>348</v>
+      <c r="D181" s="6" t="s">
+        <v>317</v>
       </c>
       <c r="E181" s="4">
-        <v>8</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>351</v>
+        <v>4</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="H181" s="6" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="182" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B182" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C182" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C182" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>352</v>
+      <c r="D182" s="6" t="s">
+        <v>318</v>
       </c>
       <c r="E182" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="G182" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="H182" s="7" t="s">
-        <v>355</v>
+        <v>8</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="183" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B183" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C183" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>356</v>
+      <c r="D183" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="E183" s="4">
-        <v>8</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="G183" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="H183" s="7" t="s">
-        <v>359</v>
+        <v>3.5</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H183" s="6" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="184" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B184" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C184" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C184" s="3" t="s">
+      <c r="D184" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E184" s="4">
+        <v>8</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G184" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D184" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="E184" s="4">
-        <v>18</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G184" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="H184" s="7" t="s">
-        <v>363</v>
+      <c r="H184" s="6" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="185" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B185" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C185" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>365</v>
+      <c r="D185" s="6" t="s">
+        <v>326</v>
       </c>
       <c r="E185" s="4">
-        <v>2</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="G185" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="H185" s="7" t="s">
-        <v>368</v>
+        <v>18</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="186" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B186" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>369</v>
+        <v>329</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>330</v>
       </c>
       <c r="E186" s="4">
         <v>2</v>
       </c>
-      <c r="F186" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="G186" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="H186" s="5" t="s">
-        <v>371</v>
+      <c r="F186" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="187" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B187" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D187" s="7" t="s">
-        <v>372</v>
+        <v>329</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="E187" s="4">
         <v>2</v>
       </c>
-      <c r="F187" s="5" t="s">
-        <v>373</v>
+      <c r="F187" s="6" t="s">
+        <v>335</v>
       </c>
       <c r="G187" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>375</v>
+        <v>335</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="188" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B188" s="3" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>376</v>
+        <v>329</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>337</v>
       </c>
       <c r="E188" s="4">
+        <v>2</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="189" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B189" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E189" s="4">
         <v>2.5</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="H188" s="5" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
-      <c r="E189" s="2"/>
-      <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
-      <c r="H189" s="1"/>
+      <c r="F189" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H189" s="6" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="190" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B190" s="1"/>
@@ -13104,6 +13133,15 @@
       <c r="G1000" s="1"/>
       <c r="H1000" s="1"/>
     </row>
+    <row r="1001" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B1001" s="1"/>
+      <c r="C1001" s="1"/>
+      <c r="D1001" s="1"/>
+      <c r="E1001" s="2"/>
+      <c r="F1001" s="1"/>
+      <c r="G1001" s="1"/>
+      <c r="H1001" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Preços P7.xlsx
+++ b/Preços P7.xlsx
@@ -1,22 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr defaultThemeVersion="153222"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="270" windowWidth="14940" windowHeight="9150" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Folha2" sheetId="1" r:id="rId4"/>
+    <sheet name="Folha2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="4cJmkQEp5ZtF5ShlA4k5nR1shmJs0Q5tTG9gyOhpOCY="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="389" count="389">
   <si>
     <t>Secção</t>
   </si>
@@ -1188,26 +1185,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
     </font>
     <font>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <name val="Arial"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1215,60 +1211,64 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1458,25 +1458,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultRowHeight="15.0" customHeight="1" defaultColWidth="12"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="14.5"/>
-    <col customWidth="1" min="3" max="3" width="14.88"/>
-    <col customWidth="1" min="4" max="4" width="20.75"/>
-    <col customWidth="1" min="6" max="6" width="26.38"/>
-    <col customWidth="1" min="7" max="7" width="31.0"/>
-    <col customWidth="1" min="8" max="8" width="26.63"/>
+    <col min="2" max="2" customWidth="1" width="14.5" style="0"/>
+    <col min="3" max="3" customWidth="1" width="14.878906" style="0"/>
+    <col min="4" max="4" customWidth="1" width="20.75" style="0"/>
+    <col min="6" max="6" customWidth="1" width="26.378906" style="0"/>
+    <col min="7" max="7" customWidth="1" width="31.0" style="0"/>
+    <col min="8" max="8" customWidth="1" width="26.628906" style="0"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="8:8" ht="15.0">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1486,7 +1486,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="8:8" ht="15.0">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="8:8" ht="15.0">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="8:8" ht="15.0">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" spans="8:8" ht="15.0">
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6">
+    <row r="6" spans="8:8" ht="15.0">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="8:8" ht="15.0">
       <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="8:8" ht="15.0">
       <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="8:8" ht="15.0">
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="8:8" ht="15.0">
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11">
+    <row r="11" spans="8:8" ht="15.0">
       <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="8:8" ht="15.0">
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13">
+    <row r="13" spans="8:8" ht="15.0">
       <c r="B13" s="4" t="s">
         <v>8</v>
       </c>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14">
+    <row r="14" spans="8:8" ht="15.0">
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" spans="8:8" ht="15.0">
       <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="8:8" ht="15.0">
       <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17">
+    <row r="17" spans="8:8" ht="15.0">
       <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="8:8" ht="15.0">
       <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" spans="8:8" ht="15.0">
       <c r="B19" s="4" t="s">
         <v>8</v>
       </c>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" spans="8:8" ht="15.0">
       <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21">
+    <row r="21" spans="8:8" ht="15.0">
       <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="8:8" ht="15.0">
       <c r="B22" s="4" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="8:8" ht="15.0">
       <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="8:8" ht="15.0">
       <c r="B24" s="4" t="s">
         <v>8</v>
       </c>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25">
+    <row r="25" spans="8:8" ht="15.0">
       <c r="B25" s="4" t="s">
         <v>8</v>
       </c>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" spans="8:8" ht="15.0">
       <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="8:8" ht="15.0">
       <c r="B27" s="4" t="s">
         <v>8</v>
       </c>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="8:8" ht="15.0">
       <c r="B28" s="4" t="s">
         <v>8</v>
       </c>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="8:8" ht="15.0">
       <c r="B29" s="4" t="s">
         <v>8</v>
       </c>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" spans="8:8" ht="15.0">
       <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="I30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" spans="8:8" ht="15.0">
       <c r="B31" s="4" t="s">
         <v>8</v>
       </c>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" spans="8:8" ht="15.0">
       <c r="B32" s="4" t="s">
         <v>8</v>
       </c>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" spans="8:8" ht="15.0">
       <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="I33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" spans="8:8" ht="15.0">
       <c r="B34" s="4" t="s">
         <v>8</v>
       </c>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="I34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" spans="8:8" ht="15.0">
       <c r="B35" s="4" t="s">
         <v>8</v>
       </c>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" spans="8:8" ht="15.0">
       <c r="B36" s="4" t="s">
         <v>8</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" spans="8:8" ht="15.0">
       <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" spans="8:8" ht="15.0">
       <c r="B38" s="4" t="s">
         <v>8</v>
       </c>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" spans="8:8" ht="15.0">
       <c r="B39" s="4" t="s">
         <v>8</v>
       </c>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" spans="8:8" ht="15.0">
       <c r="B40" s="4" t="s">
         <v>8</v>
       </c>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" spans="8:8" ht="15.0">
       <c r="B41" s="4" t="s">
         <v>8</v>
       </c>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" spans="8:8" ht="15.0">
       <c r="B42" s="4" t="s">
         <v>8</v>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" spans="8:8" ht="15.0">
       <c r="B43" s="4" t="s">
         <v>8</v>
       </c>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="I43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" spans="8:8" ht="15.0">
       <c r="B44" s="4" t="s">
         <v>8</v>
       </c>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" spans="8:8" ht="15.0">
       <c r="B45" s="4" t="s">
         <v>8</v>
       </c>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="I45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" spans="8:8" ht="15.0">
       <c r="B46" s="4" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" spans="8:8" ht="15.0">
       <c r="B47" s="4" t="s">
         <v>8</v>
       </c>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" spans="8:8" ht="15.0">
       <c r="B48" s="4" t="s">
         <v>8</v>
       </c>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="I48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" spans="8:8" ht="15.0">
       <c r="B49" s="4" t="s">
         <v>8</v>
       </c>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="I49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" spans="8:8" ht="15.0">
       <c r="B50" s="4" t="s">
         <v>8</v>
       </c>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="I50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" spans="8:8" ht="15.0">
       <c r="B51" s="4" t="s">
         <v>8</v>
       </c>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="I51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="8:8" ht="15.0">
       <c r="B52" s="4" t="s">
         <v>8</v>
       </c>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="I52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" spans="8:8" ht="15.0">
       <c r="B53" s="4" t="s">
         <v>8</v>
       </c>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" spans="8:8" ht="15.0">
       <c r="B54" s="4" t="s">
         <v>8</v>
       </c>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="I54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" spans="8:8" ht="15.0">
       <c r="B55" s="4" t="s">
         <v>8</v>
       </c>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" spans="8:8" ht="15.0">
       <c r="B56" s="4" t="s">
         <v>8</v>
       </c>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" spans="8:8" ht="15.0">
       <c r="B57" s="4" t="s">
         <v>8</v>
       </c>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="I57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" spans="8:8" ht="15.0">
       <c r="B58" s="4" t="s">
         <v>8</v>
       </c>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" spans="8:8" ht="15.0">
       <c r="B59" s="4" t="s">
         <v>8</v>
       </c>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="I59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" spans="8:8" ht="15.0">
       <c r="B60" s="4" t="s">
         <v>8</v>
       </c>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="I60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" spans="8:8" ht="15.0">
       <c r="B61" s="4" t="s">
         <v>8</v>
       </c>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" spans="8:8" ht="15.0">
       <c r="B62" s="4" t="s">
         <v>8</v>
       </c>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="I62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" spans="8:8" ht="15.0">
       <c r="B63" s="4" t="s">
         <v>8</v>
       </c>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" spans="8:8" ht="15.0">
       <c r="B64" s="4" t="s">
         <v>8</v>
       </c>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="I64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" spans="8:8" ht="15.0">
       <c r="B65" s="4" t="s">
         <v>8</v>
       </c>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" spans="8:8" ht="15.0">
       <c r="B66" s="4" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" spans="8:8" ht="15.0">
       <c r="B67" s="4" t="s">
         <v>8</v>
       </c>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" spans="8:8" ht="15.0">
       <c r="B68" s="4" t="s">
         <v>8</v>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="I68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" spans="8:8" ht="15.0">
       <c r="B69" s="4" t="s">
         <v>8</v>
       </c>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" spans="8:8" ht="15.0">
       <c r="B70" s="4" t="s">
         <v>8</v>
       </c>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" spans="8:8" ht="15.0">
       <c r="B71" s="4" t="s">
         <v>8</v>
       </c>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" spans="8:8" ht="15.0">
       <c r="B72" s="4" t="s">
         <v>8</v>
       </c>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="8:8" ht="15.0">
       <c r="B73" s="4" t="s">
         <v>8</v>
       </c>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="I73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="8:8" ht="15.0">
       <c r="B74" s="4" t="s">
         <v>8</v>
       </c>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="I74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="8:8" ht="15.0">
       <c r="B75" s="4" t="s">
         <v>187</v>
       </c>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" spans="8:8" ht="15.0">
       <c r="B76" s="4" t="s">
         <v>187</v>
       </c>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="I76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="8:8" ht="15.0">
       <c r="B77" s="4" t="s">
         <v>187</v>
       </c>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="I77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="8:8" ht="15.0">
       <c r="B78" s="4" t="s">
         <v>187</v>
       </c>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="I78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="8:8" ht="15.0">
       <c r="B79" s="4" t="s">
         <v>187</v>
       </c>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="8:8" ht="15.0">
       <c r="B80" s="4" t="s">
         <v>187</v>
       </c>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="8:8" ht="15.0">
       <c r="B81" s="4" t="s">
         <v>187</v>
       </c>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="I81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" spans="8:8" ht="15.0">
       <c r="B82" s="4" t="s">
         <v>187</v>
       </c>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="I82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" spans="8:8" ht="15.0">
       <c r="B83" s="4" t="s">
         <v>187</v>
       </c>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="I83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" spans="8:8" ht="15.0">
       <c r="B84" s="4" t="s">
         <v>187</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" spans="8:8" ht="15.0">
       <c r="B85" s="4" t="s">
         <v>187</v>
       </c>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="I85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" spans="8:8" ht="15.0">
       <c r="B86" s="4" t="s">
         <v>187</v>
       </c>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="I86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" spans="8:8" ht="15.0">
       <c r="B87" s="4" t="s">
         <v>187</v>
       </c>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="I87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" spans="8:8" ht="15.0">
       <c r="B88" s="4" t="s">
         <v>187</v>
       </c>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="I88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" spans="8:8" ht="15.0">
       <c r="B89" s="4" t="s">
         <v>187</v>
       </c>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="8:8" ht="15.0">
       <c r="B90" s="4" t="s">
         <v>187</v>
       </c>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="I90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" spans="8:8" ht="15.0">
       <c r="B91" s="4" t="s">
         <v>187</v>
       </c>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" spans="8:8" ht="15.0">
       <c r="B92" s="4" t="s">
         <v>187</v>
       </c>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="I92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" spans="8:8" ht="15.0">
       <c r="B93" s="4" t="s">
         <v>187</v>
       </c>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" spans="8:8" ht="15.0">
       <c r="B94" s="4" t="s">
         <v>187</v>
       </c>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" spans="8:8" ht="15.0">
       <c r="B95" s="4" t="s">
         <v>187</v>
       </c>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" spans="8:8" ht="15.0">
       <c r="B96" s="4" t="s">
         <v>187</v>
       </c>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="I96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" spans="8:8" ht="15.0">
       <c r="B97" s="4" t="s">
         <v>187</v>
       </c>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" spans="8:8" ht="15.0">
       <c r="B98" s="4" t="s">
         <v>187</v>
       </c>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" spans="8:8" ht="15.0">
       <c r="B99" s="4" t="s">
         <v>187</v>
       </c>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="I99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" spans="8:8" ht="15.0">
       <c r="B100" s="4" t="s">
         <v>187</v>
       </c>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="I100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" spans="8:8" ht="15.0">
       <c r="B101" s="4" t="s">
         <v>187</v>
       </c>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="I101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" spans="8:8" ht="15.0">
       <c r="B102" s="4" t="s">
         <v>187</v>
       </c>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="I102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" spans="8:8" ht="15.0">
       <c r="B103" s="4" t="s">
         <v>187</v>
       </c>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" spans="8:8" ht="15.0">
       <c r="B104" s="4" t="s">
         <v>187</v>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="I104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" spans="8:8" ht="15.0">
       <c r="B105" s="4" t="s">
         <v>187</v>
       </c>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="I105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" spans="8:8" ht="15.0">
       <c r="B106" s="4" t="s">
         <v>187</v>
       </c>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" spans="8:8" ht="15.0">
       <c r="B107" s="4" t="s">
         <v>187</v>
       </c>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="I107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" spans="8:8" ht="15.0">
       <c r="B108" s="4" t="s">
         <v>187</v>
       </c>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" spans="8:8" ht="15.0">
       <c r="B109" s="4" t="s">
         <v>187</v>
       </c>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="I109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" spans="8:8" ht="15.0">
       <c r="B110" s="4" t="s">
         <v>187</v>
       </c>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="I110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" spans="8:8" ht="15.0">
       <c r="B111" s="4" t="s">
         <v>187</v>
       </c>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="I111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" spans="8:8" ht="15.0">
       <c r="B112" s="4" t="s">
         <v>187</v>
       </c>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="I112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" spans="8:8" ht="15.0">
       <c r="B113" s="4" t="s">
         <v>187</v>
       </c>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" spans="8:8" ht="15.0">
       <c r="B114" s="4" t="s">
         <v>187</v>
       </c>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="I114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" spans="8:8" ht="15.0">
       <c r="B115" s="4" t="s">
         <v>187</v>
       </c>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" spans="8:8" ht="15.0">
       <c r="B116" s="4" t="s">
         <v>187</v>
       </c>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" spans="8:8" ht="15.0">
       <c r="B117" s="4" t="s">
         <v>187</v>
       </c>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="I117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" spans="8:8" ht="15.0">
       <c r="B118" s="4" t="s">
         <v>187</v>
       </c>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="I118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" spans="8:8" ht="15.0">
       <c r="B119" s="4" t="s">
         <v>187</v>
       </c>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="I119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" spans="8:8" ht="15.0">
       <c r="B120" s="4" t="s">
         <v>187</v>
       </c>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="I120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" spans="8:8" ht="15.0">
       <c r="B121" s="4" t="s">
         <v>187</v>
       </c>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="I121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" spans="8:8" ht="15.0">
       <c r="B122" s="4" t="s">
         <v>187</v>
       </c>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="I122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" spans="8:8" ht="15.0">
       <c r="B123" s="4" t="s">
         <v>187</v>
       </c>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" spans="8:8" ht="15.0">
       <c r="B124" s="4" t="s">
         <v>187</v>
       </c>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="I124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" spans="8:8" ht="15.0">
       <c r="B125" s="4" t="s">
         <v>187</v>
       </c>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" spans="8:8" ht="15.0">
       <c r="B126" s="4" t="s">
         <v>187</v>
       </c>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="I126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" spans="8:8" ht="15.0">
       <c r="B127" s="4" t="s">
         <v>187</v>
       </c>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" spans="8:8" ht="15.0">
       <c r="B128" s="4" t="s">
         <v>187</v>
       </c>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="I128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" spans="8:8" ht="15.0">
       <c r="B129" s="4" t="s">
         <v>187</v>
       </c>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="I129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" spans="8:8" ht="15.0">
       <c r="B130" s="4" t="s">
         <v>187</v>
       </c>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="I130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" spans="8:8" ht="15.0">
       <c r="B131" s="4" t="s">
         <v>187</v>
       </c>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="I131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" spans="8:8" ht="15.0">
       <c r="B132" s="4" t="s">
         <v>187</v>
       </c>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" spans="8:8" ht="15.0">
       <c r="B133" s="4" t="s">
         <v>187</v>
       </c>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="I133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" spans="8:8" ht="15.0">
       <c r="B134" s="4" t="s">
         <v>187</v>
       </c>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" spans="8:8" ht="15.0">
       <c r="B135" s="4" t="s">
         <v>278</v>
       </c>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="I135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" spans="8:8" ht="15.0">
       <c r="B136" s="4" t="s">
         <v>278</v>
       </c>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" spans="8:8" ht="15.0">
       <c r="B137" s="4" t="s">
         <v>278</v>
       </c>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="I137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" spans="8:8" ht="15.0">
       <c r="B138" s="4" t="s">
         <v>278</v>
       </c>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" spans="8:8" ht="15.0">
       <c r="B139" s="4" t="s">
         <v>278</v>
       </c>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" spans="8:8" ht="15.0">
       <c r="B140" s="4" t="s">
         <v>278</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="8:8" ht="15.0">
       <c r="B141" s="4" t="s">
         <v>278</v>
       </c>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="I141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" spans="8:8" ht="15.0">
       <c r="B142" s="4" t="s">
         <v>278</v>
       </c>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="I142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" spans="8:8" ht="15.0">
       <c r="B143" s="4" t="s">
         <v>278</v>
       </c>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" spans="8:8" ht="15.0">
       <c r="B144" s="4" t="s">
         <v>278</v>
       </c>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="I144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" spans="8:8" ht="15.0">
       <c r="B145" s="4" t="s">
         <v>278</v>
       </c>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="I145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" spans="8:8" ht="15.0">
       <c r="B146" s="4" t="s">
         <v>278</v>
       </c>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" spans="8:8" ht="15.0">
       <c r="B147" s="4" t="s">
         <v>278</v>
       </c>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="I147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" spans="8:8" ht="15.0">
       <c r="B148" s="4" t="s">
         <v>278</v>
       </c>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="I148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" spans="8:8" ht="15.0">
       <c r="B149" s="4" t="s">
         <v>278</v>
       </c>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="I149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" spans="8:8" ht="15.0">
       <c r="B150" s="4" t="s">
         <v>278</v>
       </c>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="I150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" spans="8:8" ht="15.0">
       <c r="B151" s="4" t="s">
         <v>278</v>
       </c>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="I151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" spans="8:8" ht="15.0">
       <c r="B152" s="4" t="s">
         <v>278</v>
       </c>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="I152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" spans="8:8" ht="15.0">
       <c r="B153" s="4" t="s">
         <v>278</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="I153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" spans="8:8" ht="15.0">
       <c r="B154" s="4" t="s">
         <v>278</v>
       </c>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="I154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" spans="8:8" ht="15.0">
       <c r="B155" s="4" t="s">
         <v>278</v>
       </c>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" spans="8:8" ht="15.0">
       <c r="B156" s="4" t="s">
         <v>278</v>
       </c>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="I156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" spans="8:8" ht="15.0">
       <c r="B157" s="4" t="s">
         <v>278</v>
       </c>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" spans="8:8" ht="15.0">
       <c r="B158" s="4" t="s">
         <v>278</v>
       </c>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="I158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" spans="8:8" ht="15.0">
       <c r="B159" s="4" t="s">
         <v>278</v>
       </c>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" spans="8:8" ht="15.0">
       <c r="B160" s="4" t="s">
         <v>278</v>
       </c>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="I160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" spans="8:8" ht="15.0">
       <c r="B161" s="4" t="s">
         <v>278</v>
       </c>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="I161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" spans="8:8" ht="15.0">
       <c r="B162" s="4" t="s">
         <v>278</v>
       </c>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="I162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" spans="8:8" ht="15.0">
       <c r="B163" s="4" t="s">
         <v>308</v>
       </c>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="I163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" spans="8:8" ht="15.0">
       <c r="B164" s="4" t="s">
         <v>308</v>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" spans="8:8" ht="15.0">
       <c r="B165" s="4" t="s">
         <v>308</v>
       </c>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="I165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" spans="8:8" ht="15.0">
       <c r="B166" s="4" t="s">
         <v>308</v>
       </c>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="I166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" spans="8:8" ht="15.0">
       <c r="B167" s="4" t="s">
         <v>308</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="I167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" spans="8:8" ht="15.0">
       <c r="B168" s="4" t="s">
         <v>308</v>
       </c>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="I168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" spans="8:8" ht="15.0">
       <c r="B169" s="4" t="s">
         <v>308</v>
       </c>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="I169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" spans="8:8" ht="15.0">
       <c r="B170" s="4" t="s">
         <v>308</v>
       </c>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" spans="8:8" ht="15.0">
       <c r="B171" s="4" t="s">
         <v>308</v>
       </c>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" spans="8:8" ht="15.0">
       <c r="B172" s="4" t="s">
         <v>308</v>
       </c>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="I172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" spans="8:8" ht="15.0">
       <c r="B173" s="4" t="s">
         <v>308</v>
       </c>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="I173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" spans="8:8" ht="15.0">
       <c r="B174" s="4" t="s">
         <v>308</v>
       </c>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="I174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" spans="8:8" ht="15.0">
       <c r="B175" s="4" t="s">
         <v>308</v>
       </c>
@@ -5664,9 +5664,11 @@
       <c r="H175" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="I175" s="3"/>
-    </row>
-    <row r="176">
+      <c r="I175" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="176" spans="8:8" ht="15.0">
       <c r="B176" s="4" t="s">
         <v>308</v>
       </c>
@@ -5690,7 +5692,7 @@
       </c>
       <c r="I176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" spans="8:8" ht="15.0">
       <c r="B177" s="4" t="s">
         <v>308</v>
       </c>
@@ -5716,7 +5718,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="8:8" ht="15.0">
       <c r="B178" s="4" t="s">
         <v>308</v>
       </c>
@@ -5742,7 +5744,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="8:8" ht="15.0">
       <c r="B179" s="4" t="s">
         <v>308</v>
       </c>
@@ -5768,7 +5770,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="8:8" ht="15.0">
       <c r="B180" s="4" t="s">
         <v>308</v>
       </c>
@@ -5792,7 +5794,7 @@
       </c>
       <c r="I180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" spans="8:8" ht="15.0">
       <c r="B181" s="4" t="s">
         <v>308</v>
       </c>
@@ -5814,9 +5816,11 @@
       <c r="H181" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="I181" s="3"/>
-    </row>
-    <row r="182">
+      <c r="I181" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="182" spans="8:8" ht="15.0">
       <c r="B182" s="4" t="s">
         <v>308</v>
       </c>
@@ -5840,7 +5844,7 @@
       </c>
       <c r="I182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" spans="8:8" ht="15.0">
       <c r="B183" s="4" t="s">
         <v>308</v>
       </c>
@@ -5866,7 +5870,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="8:8" ht="15.0">
       <c r="B184" s="4" t="s">
         <v>308</v>
       </c>
@@ -5892,7 +5896,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="8:8" ht="15.0">
       <c r="B185" s="4" t="s">
         <v>308</v>
       </c>
@@ -5918,7 +5922,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="8:8" ht="15.0">
       <c r="B186" s="4" t="s">
         <v>308</v>
       </c>
@@ -5942,7 +5946,7 @@
       </c>
       <c r="I186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" spans="8:8" ht="15.0">
       <c r="B187" s="4" t="s">
         <v>308</v>
       </c>
@@ -5966,7 +5970,7 @@
       </c>
       <c r="I187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" spans="8:8" ht="15.0">
       <c r="B188" s="4" t="s">
         <v>308</v>
       </c>
@@ -5990,7 +5994,7 @@
       </c>
       <c r="I188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" spans="8:8" ht="15.0">
       <c r="B189" s="4" t="s">
         <v>308</v>
       </c>
@@ -6014,7 +6018,7 @@
       </c>
       <c r="I189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" spans="8:8" ht="15.0">
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
@@ -6024,7 +6028,7 @@
       <c r="H190" s="1"/>
       <c r="I190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" spans="8:8" ht="15.0">
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
@@ -6034,7 +6038,7 @@
       <c r="H191" s="1"/>
       <c r="I191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" spans="8:8" ht="15.0">
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
@@ -6044,7 +6048,7 @@
       <c r="H192" s="1"/>
       <c r="I192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" spans="8:8" ht="15.0">
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
@@ -6054,7 +6058,7 @@
       <c r="H193" s="1"/>
       <c r="I193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" spans="8:8" ht="15.0">
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
@@ -6064,7 +6068,7 @@
       <c r="H194" s="1"/>
       <c r="I194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" spans="8:8" ht="15.0">
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
@@ -6074,7 +6078,7 @@
       <c r="H195" s="1"/>
       <c r="I195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" spans="8:8" ht="15.0">
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
@@ -6084,7 +6088,7 @@
       <c r="H196" s="1"/>
       <c r="I196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" spans="8:8" ht="15.0">
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
@@ -6094,7 +6098,7 @@
       <c r="H197" s="1"/>
       <c r="I197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" spans="8:8" ht="15.0">
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
@@ -6104,7 +6108,7 @@
       <c r="H198" s="1"/>
       <c r="I198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" spans="8:8" ht="15.0">
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
@@ -6114,7 +6118,7 @@
       <c r="H199" s="1"/>
       <c r="I199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" spans="8:8" ht="15.0">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
@@ -6124,7 +6128,7 @@
       <c r="H200" s="1"/>
       <c r="I200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" spans="8:8" ht="15.0">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
@@ -6134,7 +6138,7 @@
       <c r="H201" s="1"/>
       <c r="I201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" spans="8:8" ht="15.0">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
@@ -6144,7 +6148,7 @@
       <c r="H202" s="1"/>
       <c r="I202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" spans="8:8" ht="15.0">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
@@ -6154,7 +6158,7 @@
       <c r="H203" s="1"/>
       <c r="I203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" spans="8:8" ht="15.0">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
@@ -6164,7 +6168,7 @@
       <c r="H204" s="1"/>
       <c r="I204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" spans="8:8" ht="15.0">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
@@ -6174,7 +6178,7 @@
       <c r="H205" s="1"/>
       <c r="I205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" spans="8:8" ht="15.0">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
@@ -6184,7 +6188,7 @@
       <c r="H206" s="1"/>
       <c r="I206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" spans="8:8" ht="15.0">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
@@ -6194,7 +6198,7 @@
       <c r="H207" s="1"/>
       <c r="I207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" spans="8:8" ht="15.0">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
@@ -6204,7 +6208,7 @@
       <c r="H208" s="1"/>
       <c r="I208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" spans="8:8" ht="15.0">
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
@@ -6214,7 +6218,7 @@
       <c r="H209" s="1"/>
       <c r="I209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" spans="8:8" ht="15.0">
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
@@ -6224,7 +6228,7 @@
       <c r="H210" s="1"/>
       <c r="I210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" spans="8:8" ht="15.0">
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
@@ -6234,7 +6238,7 @@
       <c r="H211" s="1"/>
       <c r="I211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" spans="8:8" ht="15.0">
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
@@ -6244,7 +6248,7 @@
       <c r="H212" s="1"/>
       <c r="I212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" spans="8:8" ht="15.0">
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
@@ -6254,7 +6258,7 @@
       <c r="H213" s="1"/>
       <c r="I213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" spans="8:8" ht="15.0">
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
@@ -6264,7 +6268,7 @@
       <c r="H214" s="1"/>
       <c r="I214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" spans="8:8" ht="15.0">
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
@@ -6274,7 +6278,7 @@
       <c r="H215" s="1"/>
       <c r="I215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" spans="8:8" ht="15.0">
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
@@ -6284,7 +6288,7 @@
       <c r="H216" s="1"/>
       <c r="I216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" spans="8:8" ht="15.0">
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
@@ -6294,7 +6298,7 @@
       <c r="H217" s="1"/>
       <c r="I217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" spans="8:8" ht="15.0">
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
@@ -6304,7 +6308,7 @@
       <c r="H218" s="1"/>
       <c r="I218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" spans="8:8" ht="15.0">
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
@@ -6314,7 +6318,7 @@
       <c r="H219" s="1"/>
       <c r="I219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" spans="8:8" ht="15.0">
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
@@ -6324,7 +6328,7 @@
       <c r="H220" s="1"/>
       <c r="I220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" spans="8:8" ht="15.0">
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
@@ -6334,7 +6338,7 @@
       <c r="H221" s="1"/>
       <c r="I221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" spans="8:8" ht="15.0">
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
@@ -6344,7 +6348,7 @@
       <c r="H222" s="1"/>
       <c r="I222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" spans="8:8" ht="15.0">
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
@@ -6354,7 +6358,7 @@
       <c r="H223" s="1"/>
       <c r="I223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" spans="8:8" ht="15.0">
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
@@ -6364,7 +6368,7 @@
       <c r="H224" s="1"/>
       <c r="I224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" spans="8:8" ht="15.0">
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
@@ -6374,7 +6378,7 @@
       <c r="H225" s="1"/>
       <c r="I225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" spans="8:8" ht="15.0">
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
@@ -6384,7 +6388,7 @@
       <c r="H226" s="1"/>
       <c r="I226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" spans="8:8" ht="15.0">
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
@@ -6394,7 +6398,7 @@
       <c r="H227" s="1"/>
       <c r="I227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" spans="8:8" ht="15.0">
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
@@ -6404,7 +6408,7 @@
       <c r="H228" s="1"/>
       <c r="I228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" spans="8:8" ht="15.0">
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
@@ -6414,7 +6418,7 @@
       <c r="H229" s="1"/>
       <c r="I229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" spans="8:8" ht="15.0">
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
@@ -6424,7 +6428,7 @@
       <c r="H230" s="1"/>
       <c r="I230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" spans="8:8" ht="15.0">
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
@@ -6434,7 +6438,7 @@
       <c r="H231" s="1"/>
       <c r="I231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" spans="8:8" ht="15.0">
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
@@ -6444,7 +6448,7 @@
       <c r="H232" s="1"/>
       <c r="I232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" spans="8:8" ht="15.0">
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
@@ -6454,7 +6458,7 @@
       <c r="H233" s="1"/>
       <c r="I233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" spans="8:8" ht="15.0">
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
@@ -6464,7 +6468,7 @@
       <c r="H234" s="1"/>
       <c r="I234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" spans="8:8" ht="15.0">
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
@@ -6474,7 +6478,7 @@
       <c r="H235" s="1"/>
       <c r="I235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" spans="8:8" ht="15.0">
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
@@ -6484,7 +6488,7 @@
       <c r="H236" s="1"/>
       <c r="I236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" spans="8:8" ht="15.0">
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
@@ -6494,7 +6498,7 @@
       <c r="H237" s="1"/>
       <c r="I237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" spans="8:8" ht="15.0">
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
@@ -6504,7 +6508,7 @@
       <c r="H238" s="1"/>
       <c r="I238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" spans="8:8" ht="15.0">
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
@@ -6514,7 +6518,7 @@
       <c r="H239" s="1"/>
       <c r="I239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" spans="8:8" ht="15.0">
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
@@ -6524,7 +6528,7 @@
       <c r="H240" s="1"/>
       <c r="I240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" spans="8:8" ht="15.0">
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
@@ -6534,7 +6538,7 @@
       <c r="H241" s="1"/>
       <c r="I241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" spans="8:8" ht="15.0">
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
@@ -6544,7 +6548,7 @@
       <c r="H242" s="1"/>
       <c r="I242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" spans="8:8" ht="15.0">
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
@@ -6554,7 +6558,7 @@
       <c r="H243" s="1"/>
       <c r="I243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" spans="8:8" ht="15.0">
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
@@ -6564,7 +6568,7 @@
       <c r="H244" s="1"/>
       <c r="I244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" spans="8:8" ht="15.0">
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
@@ -6574,7 +6578,7 @@
       <c r="H245" s="1"/>
       <c r="I245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" spans="8:8" ht="15.0">
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
@@ -6584,7 +6588,7 @@
       <c r="H246" s="1"/>
       <c r="I246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" spans="8:8" ht="15.0">
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
@@ -6594,7 +6598,7 @@
       <c r="H247" s="1"/>
       <c r="I247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" spans="8:8" ht="15.0">
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
@@ -6604,7 +6608,7 @@
       <c r="H248" s="1"/>
       <c r="I248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" spans="8:8" ht="15.0">
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
@@ -6614,7 +6618,7 @@
       <c r="H249" s="1"/>
       <c r="I249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" spans="8:8" ht="15.0">
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
@@ -6624,7 +6628,7 @@
       <c r="H250" s="1"/>
       <c r="I250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" spans="8:8" ht="15.0">
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
@@ -6634,7 +6638,7 @@
       <c r="H251" s="1"/>
       <c r="I251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" spans="8:8" ht="15.0">
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
@@ -6644,7 +6648,7 @@
       <c r="H252" s="1"/>
       <c r="I252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" spans="8:8" ht="15.0">
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
@@ -6654,7 +6658,7 @@
       <c r="H253" s="1"/>
       <c r="I253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" spans="8:8" ht="15.0">
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
@@ -6664,7 +6668,7 @@
       <c r="H254" s="1"/>
       <c r="I254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" spans="8:8" ht="15.0">
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
@@ -6674,7 +6678,7 @@
       <c r="H255" s="1"/>
       <c r="I255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" spans="8:8" ht="15.0">
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
@@ -6684,7 +6688,7 @@
       <c r="H256" s="1"/>
       <c r="I256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" spans="8:8" ht="15.0">
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
@@ -6694,7 +6698,7 @@
       <c r="H257" s="1"/>
       <c r="I257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" spans="8:8" ht="15.0">
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
@@ -6704,7 +6708,7 @@
       <c r="H258" s="1"/>
       <c r="I258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" spans="8:8" ht="15.0">
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
@@ -6714,7 +6718,7 @@
       <c r="H259" s="1"/>
       <c r="I259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" spans="8:8" ht="15.0">
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
@@ -6724,7 +6728,7 @@
       <c r="H260" s="1"/>
       <c r="I260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" spans="8:8" ht="15.0">
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
@@ -6734,7 +6738,7 @@
       <c r="H261" s="1"/>
       <c r="I261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" spans="8:8" ht="15.0">
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
@@ -6744,7 +6748,7 @@
       <c r="H262" s="1"/>
       <c r="I262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" spans="8:8" ht="15.0">
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
@@ -6754,7 +6758,7 @@
       <c r="H263" s="1"/>
       <c r="I263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" spans="8:8" ht="15.0">
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
@@ -6764,7 +6768,7 @@
       <c r="H264" s="1"/>
       <c r="I264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" spans="8:8" ht="15.0">
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
@@ -6774,7 +6778,7 @@
       <c r="H265" s="1"/>
       <c r="I265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" spans="8:8" ht="15.0">
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
@@ -6784,7 +6788,7 @@
       <c r="H266" s="1"/>
       <c r="I266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" spans="8:8" ht="15.0">
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
@@ -6794,7 +6798,7 @@
       <c r="H267" s="1"/>
       <c r="I267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" spans="8:8" ht="15.0">
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
@@ -6804,7 +6808,7 @@
       <c r="H268" s="1"/>
       <c r="I268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" spans="8:8" ht="15.0">
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
@@ -6814,7 +6818,7 @@
       <c r="H269" s="1"/>
       <c r="I269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" spans="8:8" ht="15.0">
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
@@ -6824,7 +6828,7 @@
       <c r="H270" s="1"/>
       <c r="I270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" spans="8:8" ht="15.0">
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
@@ -6834,7 +6838,7 @@
       <c r="H271" s="1"/>
       <c r="I271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" spans="8:8" ht="15.0">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
@@ -6844,7 +6848,7 @@
       <c r="H272" s="1"/>
       <c r="I272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" spans="8:8" ht="15.0">
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
@@ -6854,7 +6858,7 @@
       <c r="H273" s="1"/>
       <c r="I273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" spans="8:8" ht="15.0">
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
@@ -6864,7 +6868,7 @@
       <c r="H274" s="1"/>
       <c r="I274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" spans="8:8" ht="15.0">
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
@@ -6874,7 +6878,7 @@
       <c r="H275" s="1"/>
       <c r="I275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" spans="8:8" ht="15.0">
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
@@ -6884,7 +6888,7 @@
       <c r="H276" s="1"/>
       <c r="I276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" spans="8:8" ht="15.0">
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
@@ -6894,7 +6898,7 @@
       <c r="H277" s="1"/>
       <c r="I277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" spans="8:8" ht="15.0">
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
@@ -6904,7 +6908,7 @@
       <c r="H278" s="1"/>
       <c r="I278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" spans="8:8" ht="15.0">
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
@@ -6914,7 +6918,7 @@
       <c r="H279" s="1"/>
       <c r="I279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" spans="8:8" ht="15.0">
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
@@ -6924,7 +6928,7 @@
       <c r="H280" s="1"/>
       <c r="I280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" spans="8:8" ht="15.0">
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
@@ -6934,7 +6938,7 @@
       <c r="H281" s="1"/>
       <c r="I281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" spans="8:8" ht="15.0">
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
@@ -6944,7 +6948,7 @@
       <c r="H282" s="1"/>
       <c r="I282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" spans="8:8" ht="15.0">
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
@@ -6954,7 +6958,7 @@
       <c r="H283" s="1"/>
       <c r="I283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" spans="8:8" ht="15.0">
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
@@ -6964,7 +6968,7 @@
       <c r="H284" s="1"/>
       <c r="I284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" spans="8:8" ht="15.0">
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
@@ -6974,7 +6978,7 @@
       <c r="H285" s="1"/>
       <c r="I285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" spans="8:8" ht="15.0">
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
@@ -6984,7 +6988,7 @@
       <c r="H286" s="1"/>
       <c r="I286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" spans="8:8" ht="15.0">
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
@@ -6994,7 +6998,7 @@
       <c r="H287" s="1"/>
       <c r="I287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" spans="8:8" ht="15.0">
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
@@ -7004,7 +7008,7 @@
       <c r="H288" s="1"/>
       <c r="I288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" spans="8:8" ht="15.0">
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
@@ -7014,7 +7018,7 @@
       <c r="H289" s="1"/>
       <c r="I289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" spans="8:8" ht="15.0">
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
@@ -7024,7 +7028,7 @@
       <c r="H290" s="1"/>
       <c r="I290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" spans="8:8" ht="15.0">
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
@@ -7034,7 +7038,7 @@
       <c r="H291" s="1"/>
       <c r="I291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" spans="8:8" ht="15.0">
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
@@ -7044,7 +7048,7 @@
       <c r="H292" s="1"/>
       <c r="I292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" spans="8:8" ht="15.0">
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
@@ -7054,7 +7058,7 @@
       <c r="H293" s="1"/>
       <c r="I293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" spans="8:8" ht="15.0">
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
@@ -7064,7 +7068,7 @@
       <c r="H294" s="1"/>
       <c r="I294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" spans="8:8" ht="15.0">
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
@@ -7074,7 +7078,7 @@
       <c r="H295" s="1"/>
       <c r="I295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" spans="8:8" ht="15.0">
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
@@ -7084,7 +7088,7 @@
       <c r="H296" s="1"/>
       <c r="I296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" spans="8:8" ht="15.0">
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
@@ -7094,7 +7098,7 @@
       <c r="H297" s="1"/>
       <c r="I297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" spans="8:8" ht="15.0">
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
@@ -7104,7 +7108,7 @@
       <c r="H298" s="1"/>
       <c r="I298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" spans="8:8" ht="15.0">
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
@@ -7114,7 +7118,7 @@
       <c r="H299" s="1"/>
       <c r="I299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" spans="8:8" ht="15.0">
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
@@ -7124,7 +7128,7 @@
       <c r="H300" s="1"/>
       <c r="I300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" spans="8:8" ht="15.0">
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
@@ -7134,7 +7138,7 @@
       <c r="H301" s="1"/>
       <c r="I301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" spans="8:8" ht="15.0">
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
@@ -7144,7 +7148,7 @@
       <c r="H302" s="1"/>
       <c r="I302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" spans="8:8" ht="15.0">
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
@@ -7154,7 +7158,7 @@
       <c r="H303" s="1"/>
       <c r="I303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" spans="8:8" ht="15.0">
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
@@ -7164,7 +7168,7 @@
       <c r="H304" s="1"/>
       <c r="I304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" spans="8:8" ht="15.0">
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
@@ -7174,7 +7178,7 @@
       <c r="H305" s="1"/>
       <c r="I305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" spans="8:8" ht="15.0">
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
@@ -7184,7 +7188,7 @@
       <c r="H306" s="1"/>
       <c r="I306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" spans="8:8" ht="15.0">
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
@@ -7194,7 +7198,7 @@
       <c r="H307" s="1"/>
       <c r="I307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" spans="8:8" ht="15.0">
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
@@ -7204,7 +7208,7 @@
       <c r="H308" s="1"/>
       <c r="I308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" spans="8:8" ht="15.0">
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
@@ -7214,7 +7218,7 @@
       <c r="H309" s="1"/>
       <c r="I309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" spans="8:8" ht="15.0">
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
@@ -7224,7 +7228,7 @@
       <c r="H310" s="1"/>
       <c r="I310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" spans="8:8" ht="15.0">
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
@@ -7234,7 +7238,7 @@
       <c r="H311" s="1"/>
       <c r="I311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" spans="8:8" ht="15.0">
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
@@ -7244,7 +7248,7 @@
       <c r="H312" s="1"/>
       <c r="I312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" spans="8:8" ht="15.0">
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
@@ -7254,7 +7258,7 @@
       <c r="H313" s="1"/>
       <c r="I313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" spans="8:8" ht="15.0">
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
@@ -7264,7 +7268,7 @@
       <c r="H314" s="1"/>
       <c r="I314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" spans="8:8" ht="15.0">
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
@@ -7274,7 +7278,7 @@
       <c r="H315" s="1"/>
       <c r="I315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" spans="8:8" ht="15.0">
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
@@ -7284,7 +7288,7 @@
       <c r="H316" s="1"/>
       <c r="I316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" spans="8:8" ht="15.0">
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
@@ -7294,7 +7298,7 @@
       <c r="H317" s="1"/>
       <c r="I317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" spans="8:8" ht="15.0">
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
@@ -7304,7 +7308,7 @@
       <c r="H318" s="1"/>
       <c r="I318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" spans="8:8" ht="15.0">
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
@@ -7314,7 +7318,7 @@
       <c r="H319" s="1"/>
       <c r="I319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" spans="8:8" ht="15.0">
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
@@ -7324,7 +7328,7 @@
       <c r="H320" s="1"/>
       <c r="I320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" spans="8:8" ht="15.0">
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
@@ -7334,7 +7338,7 @@
       <c r="H321" s="1"/>
       <c r="I321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" spans="8:8" ht="15.0">
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
@@ -7344,7 +7348,7 @@
       <c r="H322" s="1"/>
       <c r="I322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" spans="8:8" ht="15.0">
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
@@ -7354,7 +7358,7 @@
       <c r="H323" s="1"/>
       <c r="I323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" spans="8:8" ht="15.0">
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
@@ -7364,7 +7368,7 @@
       <c r="H324" s="1"/>
       <c r="I324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" spans="8:8" ht="15.0">
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
@@ -7374,7 +7378,7 @@
       <c r="H325" s="1"/>
       <c r="I325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" spans="8:8" ht="15.0">
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
@@ -7384,7 +7388,7 @@
       <c r="H326" s="1"/>
       <c r="I326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" spans="8:8" ht="15.0">
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
@@ -7394,7 +7398,7 @@
       <c r="H327" s="1"/>
       <c r="I327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" spans="8:8" ht="15.0">
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
@@ -7404,7 +7408,7 @@
       <c r="H328" s="1"/>
       <c r="I328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" spans="8:8" ht="15.0">
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
@@ -7414,7 +7418,7 @@
       <c r="H329" s="1"/>
       <c r="I329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" spans="8:8" ht="15.0">
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
@@ -7424,7 +7428,7 @@
       <c r="H330" s="1"/>
       <c r="I330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" spans="8:8" ht="15.0">
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
@@ -7434,7 +7438,7 @@
       <c r="H331" s="1"/>
       <c r="I331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" spans="8:8" ht="15.0">
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
@@ -7444,7 +7448,7 @@
       <c r="H332" s="1"/>
       <c r="I332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" spans="8:8" ht="15.0">
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
@@ -7454,7 +7458,7 @@
       <c r="H333" s="1"/>
       <c r="I333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" spans="8:8" ht="15.0">
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
@@ -7464,7 +7468,7 @@
       <c r="H334" s="1"/>
       <c r="I334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" spans="8:8" ht="15.0">
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
@@ -7474,7 +7478,7 @@
       <c r="H335" s="1"/>
       <c r="I335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" spans="8:8" ht="15.0">
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
@@ -7484,7 +7488,7 @@
       <c r="H336" s="1"/>
       <c r="I336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" spans="8:8" ht="15.0">
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
@@ -7494,7 +7498,7 @@
       <c r="H337" s="1"/>
       <c r="I337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" spans="8:8" ht="15.0">
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
@@ -7504,7 +7508,7 @@
       <c r="H338" s="1"/>
       <c r="I338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" spans="8:8" ht="15.0">
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
@@ -7514,7 +7518,7 @@
       <c r="H339" s="1"/>
       <c r="I339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" spans="8:8" ht="15.0">
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
@@ -7524,7 +7528,7 @@
       <c r="H340" s="1"/>
       <c r="I340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" spans="8:8" ht="15.0">
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
@@ -7534,7 +7538,7 @@
       <c r="H341" s="1"/>
       <c r="I341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" spans="8:8" ht="15.0">
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
@@ -7544,7 +7548,7 @@
       <c r="H342" s="1"/>
       <c r="I342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" spans="8:8" ht="15.0">
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
@@ -7554,7 +7558,7 @@
       <c r="H343" s="1"/>
       <c r="I343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" spans="8:8" ht="15.0">
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
@@ -7564,7 +7568,7 @@
       <c r="H344" s="1"/>
       <c r="I344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" spans="8:8" ht="15.0">
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
@@ -7574,7 +7578,7 @@
       <c r="H345" s="1"/>
       <c r="I345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" spans="8:8" ht="15.0">
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
@@ -7584,7 +7588,7 @@
       <c r="H346" s="1"/>
       <c r="I346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" spans="8:8" ht="15.0">
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
@@ -7594,7 +7598,7 @@
       <c r="H347" s="1"/>
       <c r="I347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" spans="8:8" ht="15.0">
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
@@ -7604,7 +7608,7 @@
       <c r="H348" s="1"/>
       <c r="I348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" spans="8:8" ht="15.0">
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
@@ -7614,7 +7618,7 @@
       <c r="H349" s="1"/>
       <c r="I349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" spans="8:8" ht="15.0">
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
@@ -7624,7 +7628,7 @@
       <c r="H350" s="1"/>
       <c r="I350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" spans="8:8" ht="15.0">
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
@@ -7634,7 +7638,7 @@
       <c r="H351" s="1"/>
       <c r="I351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" spans="8:8" ht="15.0">
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
@@ -7644,7 +7648,7 @@
       <c r="H352" s="1"/>
       <c r="I352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" spans="8:8" ht="15.0">
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
@@ -7654,7 +7658,7 @@
       <c r="H353" s="1"/>
       <c r="I353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" spans="8:8" ht="15.0">
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
@@ -7664,7 +7668,7 @@
       <c r="H354" s="1"/>
       <c r="I354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" spans="8:8" ht="15.0">
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
@@ -7674,7 +7678,7 @@
       <c r="H355" s="1"/>
       <c r="I355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" spans="8:8" ht="15.0">
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
@@ -7684,7 +7688,7 @@
       <c r="H356" s="1"/>
       <c r="I356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" spans="8:8" ht="15.0">
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
@@ -7694,7 +7698,7 @@
       <c r="H357" s="1"/>
       <c r="I357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" spans="8:8" ht="15.0">
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
@@ -7704,7 +7708,7 @@
       <c r="H358" s="1"/>
       <c r="I358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" spans="8:8" ht="15.0">
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
@@ -7714,7 +7718,7 @@
       <c r="H359" s="1"/>
       <c r="I359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" spans="8:8" ht="15.0">
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
@@ -7724,7 +7728,7 @@
       <c r="H360" s="1"/>
       <c r="I360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" spans="8:8" ht="15.0">
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
@@ -7734,7 +7738,7 @@
       <c r="H361" s="1"/>
       <c r="I361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" spans="8:8" ht="15.0">
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
@@ -7744,7 +7748,7 @@
       <c r="H362" s="1"/>
       <c r="I362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" spans="8:8" ht="15.0">
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
@@ -7754,7 +7758,7 @@
       <c r="H363" s="1"/>
       <c r="I363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" spans="8:8" ht="15.0">
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
       <c r="D364" s="1"/>
@@ -7764,7 +7768,7 @@
       <c r="H364" s="1"/>
       <c r="I364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" spans="8:8" ht="15.0">
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
       <c r="D365" s="1"/>
@@ -7774,7 +7778,7 @@
       <c r="H365" s="1"/>
       <c r="I365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" spans="8:8" ht="15.0">
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
       <c r="D366" s="1"/>
@@ -7784,7 +7788,7 @@
       <c r="H366" s="1"/>
       <c r="I366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" spans="8:8" ht="15.0">
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
       <c r="D367" s="1"/>
@@ -7794,7 +7798,7 @@
       <c r="H367" s="1"/>
       <c r="I367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" spans="8:8" ht="15.0">
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
       <c r="D368" s="1"/>
@@ -7804,7 +7808,7 @@
       <c r="H368" s="1"/>
       <c r="I368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" spans="8:8" ht="15.0">
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
       <c r="D369" s="1"/>
@@ -7814,7 +7818,7 @@
       <c r="H369" s="1"/>
       <c r="I369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" spans="8:8" ht="15.0">
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
       <c r="D370" s="1"/>
@@ -7824,7 +7828,7 @@
       <c r="H370" s="1"/>
       <c r="I370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" spans="8:8" ht="15.0">
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
       <c r="D371" s="1"/>
@@ -7834,7 +7838,7 @@
       <c r="H371" s="1"/>
       <c r="I371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" spans="8:8" ht="15.0">
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
       <c r="D372" s="1"/>
@@ -7844,7 +7848,7 @@
       <c r="H372" s="1"/>
       <c r="I372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" spans="8:8" ht="15.0">
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
       <c r="D373" s="1"/>
@@ -7854,7 +7858,7 @@
       <c r="H373" s="1"/>
       <c r="I373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" spans="8:8" ht="15.0">
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
       <c r="D374" s="1"/>
@@ -7864,7 +7868,7 @@
       <c r="H374" s="1"/>
       <c r="I374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" spans="8:8" ht="15.0">
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
       <c r="D375" s="1"/>
@@ -7874,7 +7878,7 @@
       <c r="H375" s="1"/>
       <c r="I375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" spans="8:8" ht="15.0">
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
       <c r="D376" s="1"/>
@@ -7884,7 +7888,7 @@
       <c r="H376" s="1"/>
       <c r="I376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" spans="8:8" ht="15.0">
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
       <c r="D377" s="1"/>
@@ -7894,7 +7898,7 @@
       <c r="H377" s="1"/>
       <c r="I377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" spans="8:8" ht="15.0">
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
       <c r="D378" s="1"/>
@@ -7904,7 +7908,7 @@
       <c r="H378" s="1"/>
       <c r="I378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" spans="8:8" ht="15.0">
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
       <c r="D379" s="1"/>
@@ -7914,7 +7918,7 @@
       <c r="H379" s="1"/>
       <c r="I379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" spans="8:8" ht="15.0">
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
       <c r="D380" s="1"/>
@@ -7924,7 +7928,7 @@
       <c r="H380" s="1"/>
       <c r="I380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" spans="8:8" ht="15.0">
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
       <c r="D381" s="1"/>
@@ -7934,7 +7938,7 @@
       <c r="H381" s="1"/>
       <c r="I381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" spans="8:8" ht="15.0">
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
       <c r="D382" s="1"/>
@@ -7944,7 +7948,7 @@
       <c r="H382" s="1"/>
       <c r="I382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" spans="8:8" ht="15.0">
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
       <c r="D383" s="1"/>
@@ -7954,7 +7958,7 @@
       <c r="H383" s="1"/>
       <c r="I383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" spans="8:8" ht="15.0">
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
       <c r="D384" s="1"/>
@@ -7964,7 +7968,7 @@
       <c r="H384" s="1"/>
       <c r="I384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" spans="8:8" ht="15.0">
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
       <c r="D385" s="1"/>
@@ -7974,7 +7978,7 @@
       <c r="H385" s="1"/>
       <c r="I385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" spans="8:8" ht="15.0">
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
       <c r="D386" s="1"/>
@@ -7984,7 +7988,7 @@
       <c r="H386" s="1"/>
       <c r="I386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" spans="8:8" ht="15.0">
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
       <c r="D387" s="1"/>
@@ -7994,7 +7998,7 @@
       <c r="H387" s="1"/>
       <c r="I387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" spans="8:8" ht="15.0">
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
       <c r="D388" s="1"/>
@@ -8004,7 +8008,7 @@
       <c r="H388" s="1"/>
       <c r="I388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" spans="8:8" ht="15.0">
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
       <c r="D389" s="1"/>
@@ -8014,7 +8018,7 @@
       <c r="H389" s="1"/>
       <c r="I389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" spans="8:8" ht="15.0">
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
       <c r="D390" s="1"/>
@@ -8024,7 +8028,7 @@
       <c r="H390" s="1"/>
       <c r="I390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" spans="8:8" ht="15.0">
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
       <c r="D391" s="1"/>
@@ -8034,7 +8038,7 @@
       <c r="H391" s="1"/>
       <c r="I391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" spans="8:8" ht="15.0">
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
       <c r="D392" s="1"/>
@@ -8044,7 +8048,7 @@
       <c r="H392" s="1"/>
       <c r="I392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" spans="8:8" ht="15.0">
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
       <c r="D393" s="1"/>
@@ -8054,7 +8058,7 @@
       <c r="H393" s="1"/>
       <c r="I393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" spans="8:8" ht="15.0">
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
       <c r="D394" s="1"/>
@@ -8064,7 +8068,7 @@
       <c r="H394" s="1"/>
       <c r="I394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" spans="8:8" ht="15.0">
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
       <c r="D395" s="1"/>
@@ -8074,7 +8078,7 @@
       <c r="H395" s="1"/>
       <c r="I395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" spans="8:8" ht="15.0">
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
       <c r="D396" s="1"/>
@@ -8084,7 +8088,7 @@
       <c r="H396" s="1"/>
       <c r="I396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" spans="8:8" ht="15.0">
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
       <c r="D397" s="1"/>
@@ -8094,7 +8098,7 @@
       <c r="H397" s="1"/>
       <c r="I397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" spans="8:8" ht="15.0">
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
       <c r="D398" s="1"/>
@@ -8104,7 +8108,7 @@
       <c r="H398" s="1"/>
       <c r="I398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" spans="8:8" ht="15.0">
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
       <c r="D399" s="1"/>
@@ -8114,7 +8118,7 @@
       <c r="H399" s="1"/>
       <c r="I399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" spans="8:8" ht="15.0">
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
       <c r="D400" s="1"/>
@@ -8124,7 +8128,7 @@
       <c r="H400" s="1"/>
       <c r="I400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" spans="8:8" ht="15.0">
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
       <c r="D401" s="1"/>
@@ -8134,7 +8138,7 @@
       <c r="H401" s="1"/>
       <c r="I401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" spans="8:8" ht="15.0">
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
       <c r="D402" s="1"/>
@@ -8144,7 +8148,7 @@
       <c r="H402" s="1"/>
       <c r="I402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" spans="8:8" ht="15.0">
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
       <c r="D403" s="1"/>
@@ -8154,7 +8158,7 @@
       <c r="H403" s="1"/>
       <c r="I403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" spans="8:8" ht="15.0">
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
       <c r="D404" s="1"/>
@@ -8164,7 +8168,7 @@
       <c r="H404" s="1"/>
       <c r="I404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" spans="8:8" ht="15.0">
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
       <c r="D405" s="1"/>
@@ -8174,7 +8178,7 @@
       <c r="H405" s="1"/>
       <c r="I405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" spans="8:8" ht="15.0">
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
       <c r="D406" s="1"/>
@@ -8184,7 +8188,7 @@
       <c r="H406" s="1"/>
       <c r="I406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" spans="8:8" ht="15.0">
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
       <c r="D407" s="1"/>
@@ -8194,7 +8198,7 @@
       <c r="H407" s="1"/>
       <c r="I407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" spans="8:8" ht="15.0">
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
       <c r="D408" s="1"/>
@@ -8204,7 +8208,7 @@
       <c r="H408" s="1"/>
       <c r="I408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" spans="8:8" ht="15.0">
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
       <c r="D409" s="1"/>
@@ -8214,7 +8218,7 @@
       <c r="H409" s="1"/>
       <c r="I409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" spans="8:8" ht="15.0">
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
       <c r="D410" s="1"/>
@@ -8224,7 +8228,7 @@
       <c r="H410" s="1"/>
       <c r="I410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" spans="8:8" ht="15.0">
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
       <c r="D411" s="1"/>
@@ -8234,7 +8238,7 @@
       <c r="H411" s="1"/>
       <c r="I411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" spans="8:8" ht="15.0">
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
       <c r="D412" s="1"/>
@@ -8244,7 +8248,7 @@
       <c r="H412" s="1"/>
       <c r="I412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" spans="8:8" ht="15.0">
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
       <c r="D413" s="1"/>
@@ -8254,7 +8258,7 @@
       <c r="H413" s="1"/>
       <c r="I413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" spans="8:8" ht="15.0">
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
       <c r="D414" s="1"/>
@@ -8264,7 +8268,7 @@
       <c r="H414" s="1"/>
       <c r="I414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" spans="8:8" ht="15.0">
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
       <c r="D415" s="1"/>
@@ -8274,7 +8278,7 @@
       <c r="H415" s="1"/>
       <c r="I415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" spans="8:8" ht="15.0">
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
       <c r="D416" s="1"/>
@@ -8284,7 +8288,7 @@
       <c r="H416" s="1"/>
       <c r="I416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" spans="8:8" ht="15.0">
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
       <c r="D417" s="1"/>
@@ -8294,7 +8298,7 @@
       <c r="H417" s="1"/>
       <c r="I417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" spans="8:8" ht="15.0">
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
       <c r="D418" s="1"/>
@@ -8304,7 +8308,7 @@
       <c r="H418" s="1"/>
       <c r="I418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" spans="8:8" ht="15.0">
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
       <c r="D419" s="1"/>
@@ -8314,7 +8318,7 @@
       <c r="H419" s="1"/>
       <c r="I419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" spans="8:8" ht="15.0">
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
       <c r="D420" s="1"/>
@@ -8324,7 +8328,7 @@
       <c r="H420" s="1"/>
       <c r="I420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" spans="8:8" ht="15.0">
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
       <c r="D421" s="1"/>
@@ -8334,7 +8338,7 @@
       <c r="H421" s="1"/>
       <c r="I421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" spans="8:8" ht="15.0">
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
       <c r="D422" s="1"/>
@@ -8344,7 +8348,7 @@
       <c r="H422" s="1"/>
       <c r="I422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" spans="8:8" ht="15.0">
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
       <c r="D423" s="1"/>
@@ -8354,7 +8358,7 @@
       <c r="H423" s="1"/>
       <c r="I423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" spans="8:8" ht="15.0">
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
       <c r="D424" s="1"/>
@@ -8364,7 +8368,7 @@
       <c r="H424" s="1"/>
       <c r="I424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" spans="8:8" ht="15.0">
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
       <c r="D425" s="1"/>
@@ -8374,7 +8378,7 @@
       <c r="H425" s="1"/>
       <c r="I425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" spans="8:8" ht="15.0">
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
       <c r="D426" s="1"/>
@@ -8384,7 +8388,7 @@
       <c r="H426" s="1"/>
       <c r="I426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" spans="8:8" ht="15.0">
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
       <c r="D427" s="1"/>
@@ -8394,7 +8398,7 @@
       <c r="H427" s="1"/>
       <c r="I427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" spans="8:8" ht="15.0">
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
       <c r="D428" s="1"/>
@@ -8404,7 +8408,7 @@
       <c r="H428" s="1"/>
       <c r="I428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" spans="8:8" ht="15.0">
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
       <c r="D429" s="1"/>
@@ -8414,7 +8418,7 @@
       <c r="H429" s="1"/>
       <c r="I429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" spans="8:8" ht="15.0">
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
       <c r="D430" s="1"/>
@@ -8424,7 +8428,7 @@
       <c r="H430" s="1"/>
       <c r="I430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" spans="8:8" ht="15.0">
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
       <c r="D431" s="1"/>
@@ -8434,7 +8438,7 @@
       <c r="H431" s="1"/>
       <c r="I431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" spans="8:8" ht="15.0">
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
       <c r="D432" s="1"/>
@@ -8444,7 +8448,7 @@
       <c r="H432" s="1"/>
       <c r="I432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" spans="8:8" ht="15.0">
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
       <c r="D433" s="1"/>
@@ -8454,7 +8458,7 @@
       <c r="H433" s="1"/>
       <c r="I433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" spans="8:8" ht="15.0">
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
       <c r="D434" s="1"/>
@@ -8464,7 +8468,7 @@
       <c r="H434" s="1"/>
       <c r="I434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" spans="8:8" ht="15.0">
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
       <c r="D435" s="1"/>
@@ -8474,7 +8478,7 @@
       <c r="H435" s="1"/>
       <c r="I435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" spans="8:8" ht="15.0">
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
@@ -8484,7 +8488,7 @@
       <c r="H436" s="1"/>
       <c r="I436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" spans="8:8" ht="15.0">
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
@@ -8494,7 +8498,7 @@
       <c r="H437" s="1"/>
       <c r="I437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" spans="8:8" ht="15.0">
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
@@ -8504,7 +8508,7 @@
       <c r="H438" s="1"/>
       <c r="I438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" spans="8:8" ht="15.0">
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
@@ -8514,7 +8518,7 @@
       <c r="H439" s="1"/>
       <c r="I439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" spans="8:8" ht="15.0">
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
@@ -8524,7 +8528,7 @@
       <c r="H440" s="1"/>
       <c r="I440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" spans="8:8" ht="15.0">
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
@@ -8534,7 +8538,7 @@
       <c r="H441" s="1"/>
       <c r="I441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" spans="8:8" ht="15.0">
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
@@ -8544,7 +8548,7 @@
       <c r="H442" s="1"/>
       <c r="I442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" spans="8:8" ht="15.0">
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
@@ -8554,7 +8558,7 @@
       <c r="H443" s="1"/>
       <c r="I443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" spans="8:8" ht="15.0">
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
@@ -8564,7 +8568,7 @@
       <c r="H444" s="1"/>
       <c r="I444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" spans="8:8" ht="15.0">
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
@@ -8574,7 +8578,7 @@
       <c r="H445" s="1"/>
       <c r="I445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" spans="8:8" ht="15.0">
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
@@ -8584,7 +8588,7 @@
       <c r="H446" s="1"/>
       <c r="I446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" spans="8:8" ht="15.0">
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
@@ -8594,7 +8598,7 @@
       <c r="H447" s="1"/>
       <c r="I447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" spans="8:8" ht="15.0">
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
@@ -8604,7 +8608,7 @@
       <c r="H448" s="1"/>
       <c r="I448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" spans="8:8" ht="15.0">
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
@@ -8614,7 +8618,7 @@
       <c r="H449" s="1"/>
       <c r="I449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" spans="8:8" ht="15.0">
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
@@ -8624,7 +8628,7 @@
       <c r="H450" s="1"/>
       <c r="I450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" spans="8:8" ht="15.0">
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
@@ -8634,7 +8638,7 @@
       <c r="H451" s="1"/>
       <c r="I451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" spans="8:8" ht="15.0">
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
@@ -8644,7 +8648,7 @@
       <c r="H452" s="1"/>
       <c r="I452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" spans="8:8" ht="15.0">
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
@@ -8654,7 +8658,7 @@
       <c r="H453" s="1"/>
       <c r="I453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" spans="8:8" ht="15.0">
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
@@ -8664,7 +8668,7 @@
       <c r="H454" s="1"/>
       <c r="I454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" spans="8:8" ht="15.0">
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
@@ -8674,7 +8678,7 @@
       <c r="H455" s="1"/>
       <c r="I455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" spans="8:8" ht="15.0">
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
@@ -8684,7 +8688,7 @@
       <c r="H456" s="1"/>
       <c r="I456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" spans="8:8" ht="15.0">
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
@@ -8694,7 +8698,7 @@
       <c r="H457" s="1"/>
       <c r="I457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" spans="8:8" ht="15.0">
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
@@ -8704,7 +8708,7 @@
       <c r="H458" s="1"/>
       <c r="I458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" spans="8:8" ht="15.0">
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
@@ -8714,7 +8718,7 @@
       <c r="H459" s="1"/>
       <c r="I459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" spans="8:8" ht="15.0">
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
@@ -8724,7 +8728,7 @@
       <c r="H460" s="1"/>
       <c r="I460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" spans="8:8" ht="15.0">
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
@@ -8734,7 +8738,7 @@
       <c r="H461" s="1"/>
       <c r="I461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" spans="8:8" ht="15.0">
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
@@ -8744,7 +8748,7 @@
       <c r="H462" s="1"/>
       <c r="I462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" spans="8:8" ht="15.0">
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
@@ -8754,7 +8758,7 @@
       <c r="H463" s="1"/>
       <c r="I463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" spans="8:8" ht="15.0">
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
@@ -8764,7 +8768,7 @@
       <c r="H464" s="1"/>
       <c r="I464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" spans="8:8" ht="15.0">
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
@@ -8774,7 +8778,7 @@
       <c r="H465" s="1"/>
       <c r="I465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" spans="8:8" ht="15.0">
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
@@ -8784,7 +8788,7 @@
       <c r="H466" s="1"/>
       <c r="I466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" spans="8:8" ht="15.0">
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
@@ -8794,7 +8798,7 @@
       <c r="H467" s="1"/>
       <c r="I467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" spans="8:8" ht="15.0">
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
@@ -8804,7 +8808,7 @@
       <c r="H468" s="1"/>
       <c r="I468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" spans="8:8" ht="15.0">
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
       <c r="D469" s="1"/>
@@ -8814,7 +8818,7 @@
       <c r="H469" s="1"/>
       <c r="I469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" spans="8:8" ht="15.0">
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
@@ -8824,7 +8828,7 @@
       <c r="H470" s="1"/>
       <c r="I470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" spans="8:8" ht="15.0">
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
@@ -8834,7 +8838,7 @@
       <c r="H471" s="1"/>
       <c r="I471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" spans="8:8" ht="15.0">
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
@@ -8844,7 +8848,7 @@
       <c r="H472" s="1"/>
       <c r="I472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" spans="8:8" ht="15.0">
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
@@ -8854,7 +8858,7 @@
       <c r="H473" s="1"/>
       <c r="I473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" spans="8:8" ht="15.0">
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
@@ -8864,7 +8868,7 @@
       <c r="H474" s="1"/>
       <c r="I474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" spans="8:8" ht="15.0">
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
@@ -8874,7 +8878,7 @@
       <c r="H475" s="1"/>
       <c r="I475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" spans="8:8" ht="15.0">
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
       <c r="D476" s="1"/>
@@ -8884,7 +8888,7 @@
       <c r="H476" s="1"/>
       <c r="I476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" spans="8:8" ht="15.0">
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
       <c r="D477" s="1"/>
@@ -8894,7 +8898,7 @@
       <c r="H477" s="1"/>
       <c r="I477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" spans="8:8" ht="15.0">
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
       <c r="D478" s="1"/>
@@ -8904,7 +8908,7 @@
       <c r="H478" s="1"/>
       <c r="I478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" spans="8:8" ht="15.0">
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
       <c r="D479" s="1"/>
@@ -8914,7 +8918,7 @@
       <c r="H479" s="1"/>
       <c r="I479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" spans="8:8" ht="15.0">
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
       <c r="D480" s="1"/>
@@ -8924,7 +8928,7 @@
       <c r="H480" s="1"/>
       <c r="I480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" spans="8:8" ht="15.0">
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
       <c r="D481" s="1"/>
@@ -8934,7 +8938,7 @@
       <c r="H481" s="1"/>
       <c r="I481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" spans="8:8" ht="15.0">
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
       <c r="D482" s="1"/>
@@ -8944,7 +8948,7 @@
       <c r="H482" s="1"/>
       <c r="I482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" spans="8:8" ht="15.0">
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
       <c r="D483" s="1"/>
@@ -8954,7 +8958,7 @@
       <c r="H483" s="1"/>
       <c r="I483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" spans="8:8" ht="15.0">
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
       <c r="D484" s="1"/>
@@ -8964,7 +8968,7 @@
       <c r="H484" s="1"/>
       <c r="I484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" spans="8:8" ht="15.0">
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
       <c r="D485" s="1"/>
@@ -8974,7 +8978,7 @@
       <c r="H485" s="1"/>
       <c r="I485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" spans="8:8" ht="15.0">
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
       <c r="D486" s="1"/>
@@ -8984,7 +8988,7 @@
       <c r="H486" s="1"/>
       <c r="I486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" spans="8:8" ht="15.0">
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
       <c r="D487" s="1"/>
@@ -8994,7 +8998,7 @@
       <c r="H487" s="1"/>
       <c r="I487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" spans="8:8" ht="15.0">
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
       <c r="D488" s="1"/>
@@ -9004,7 +9008,7 @@
       <c r="H488" s="1"/>
       <c r="I488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" spans="8:8" ht="15.0">
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
       <c r="D489" s="1"/>
@@ -9014,7 +9018,7 @@
       <c r="H489" s="1"/>
       <c r="I489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" spans="8:8" ht="15.0">
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
       <c r="D490" s="1"/>
@@ -9024,7 +9028,7 @@
       <c r="H490" s="1"/>
       <c r="I490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" spans="8:8" ht="15.0">
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
       <c r="D491" s="1"/>
@@ -9034,7 +9038,7 @@
       <c r="H491" s="1"/>
       <c r="I491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" spans="8:8" ht="15.0">
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
       <c r="D492" s="1"/>
@@ -9044,7 +9048,7 @@
       <c r="H492" s="1"/>
       <c r="I492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" spans="8:8" ht="15.0">
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
       <c r="D493" s="1"/>
@@ -9054,7 +9058,7 @@
       <c r="H493" s="1"/>
       <c r="I493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" spans="8:8" ht="15.0">
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
       <c r="D494" s="1"/>
@@ -9064,7 +9068,7 @@
       <c r="H494" s="1"/>
       <c r="I494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" spans="8:8" ht="15.0">
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
       <c r="D495" s="1"/>
@@ -9074,7 +9078,7 @@
       <c r="H495" s="1"/>
       <c r="I495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" spans="8:8" ht="15.0">
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
       <c r="D496" s="1"/>
@@ -9084,7 +9088,7 @@
       <c r="H496" s="1"/>
       <c r="I496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" spans="8:8" ht="15.0">
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
       <c r="D497" s="1"/>
@@ -9094,7 +9098,7 @@
       <c r="H497" s="1"/>
       <c r="I497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" spans="8:8" ht="15.0">
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
       <c r="D498" s="1"/>
@@ -9104,7 +9108,7 @@
       <c r="H498" s="1"/>
       <c r="I498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" spans="8:8" ht="15.0">
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
       <c r="D499" s="1"/>
@@ -9114,7 +9118,7 @@
       <c r="H499" s="1"/>
       <c r="I499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" spans="8:8" ht="15.0">
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
       <c r="D500" s="1"/>
@@ -9124,7 +9128,7 @@
       <c r="H500" s="1"/>
       <c r="I500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" spans="8:8" ht="15.0">
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
       <c r="D501" s="1"/>
@@ -9134,7 +9138,7 @@
       <c r="H501" s="1"/>
       <c r="I501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" spans="8:8" ht="15.0">
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
       <c r="D502" s="1"/>
@@ -9144,7 +9148,7 @@
       <c r="H502" s="1"/>
       <c r="I502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" spans="8:8" ht="15.0">
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
       <c r="D503" s="1"/>
@@ -9154,7 +9158,7 @@
       <c r="H503" s="1"/>
       <c r="I503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" spans="8:8" ht="15.0">
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
       <c r="D504" s="1"/>
@@ -9164,7 +9168,7 @@
       <c r="H504" s="1"/>
       <c r="I504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" spans="8:8" ht="15.0">
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
       <c r="D505" s="1"/>
@@ -9174,7 +9178,7 @@
       <c r="H505" s="1"/>
       <c r="I505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" spans="8:8" ht="15.0">
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
       <c r="D506" s="1"/>
@@ -9184,7 +9188,7 @@
       <c r="H506" s="1"/>
       <c r="I506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" spans="8:8" ht="15.0">
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
       <c r="D507" s="1"/>
@@ -9194,7 +9198,7 @@
       <c r="H507" s="1"/>
       <c r="I507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" spans="8:8" ht="15.0">
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
       <c r="D508" s="1"/>
@@ -9204,7 +9208,7 @@
       <c r="H508" s="1"/>
       <c r="I508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" spans="8:8" ht="15.0">
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
       <c r="D509" s="1"/>
@@ -9214,7 +9218,7 @@
       <c r="H509" s="1"/>
       <c r="I509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" spans="8:8" ht="15.0">
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
       <c r="D510" s="1"/>
@@ -9224,7 +9228,7 @@
       <c r="H510" s="1"/>
       <c r="I510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" spans="8:8" ht="15.0">
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
       <c r="D511" s="1"/>
@@ -9234,7 +9238,7 @@
       <c r="H511" s="1"/>
       <c r="I511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" spans="8:8" ht="15.0">
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
       <c r="D512" s="1"/>
@@ -9244,7 +9248,7 @@
       <c r="H512" s="1"/>
       <c r="I512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" spans="8:8" ht="15.0">
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
       <c r="D513" s="1"/>
@@ -9254,7 +9258,7 @@
       <c r="H513" s="1"/>
       <c r="I513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" spans="8:8" ht="15.0">
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
       <c r="D514" s="1"/>
@@ -9264,7 +9268,7 @@
       <c r="H514" s="1"/>
       <c r="I514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" spans="8:8" ht="15.0">
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
       <c r="D515" s="1"/>
@@ -9274,7 +9278,7 @@
       <c r="H515" s="1"/>
       <c r="I515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" spans="8:8" ht="15.0">
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
       <c r="D516" s="1"/>
@@ -9284,7 +9288,7 @@
       <c r="H516" s="1"/>
       <c r="I516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" spans="8:8" ht="15.0">
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
       <c r="D517" s="1"/>
@@ -9294,7 +9298,7 @@
       <c r="H517" s="1"/>
       <c r="I517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" spans="8:8" ht="15.0">
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
       <c r="D518" s="1"/>
@@ -9304,7 +9308,7 @@
       <c r="H518" s="1"/>
       <c r="I518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" spans="8:8" ht="15.0">
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
       <c r="D519" s="1"/>
@@ -9314,7 +9318,7 @@
       <c r="H519" s="1"/>
       <c r="I519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" spans="8:8" ht="15.0">
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
       <c r="D520" s="1"/>
@@ -9324,7 +9328,7 @@
       <c r="H520" s="1"/>
       <c r="I520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" spans="8:8" ht="15.0">
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
       <c r="D521" s="1"/>
@@ -9334,7 +9338,7 @@
       <c r="H521" s="1"/>
       <c r="I521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" spans="8:8" ht="15.0">
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
       <c r="D522" s="1"/>
@@ -9344,7 +9348,7 @@
       <c r="H522" s="1"/>
       <c r="I522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" spans="8:8" ht="15.0">
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
@@ -9354,7 +9358,7 @@
       <c r="H523" s="1"/>
       <c r="I523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" spans="8:8" ht="15.0">
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
       <c r="D524" s="1"/>
@@ -9364,7 +9368,7 @@
       <c r="H524" s="1"/>
       <c r="I524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" spans="8:8" ht="15.0">
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
@@ -9374,7 +9378,7 @@
       <c r="H525" s="1"/>
       <c r="I525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" spans="8:8" ht="15.0">
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
       <c r="D526" s="1"/>
@@ -9384,7 +9388,7 @@
       <c r="H526" s="1"/>
       <c r="I526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" spans="8:8" ht="15.0">
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
       <c r="D527" s="1"/>
@@ -9394,7 +9398,7 @@
       <c r="H527" s="1"/>
       <c r="I527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" spans="8:8" ht="15.0">
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
       <c r="D528" s="1"/>
@@ -9404,7 +9408,7 @@
       <c r="H528" s="1"/>
       <c r="I528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" spans="8:8" ht="15.0">
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
       <c r="D529" s="1"/>
@@ -9414,7 +9418,7 @@
       <c r="H529" s="1"/>
       <c r="I529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" spans="8:8" ht="15.0">
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
       <c r="D530" s="1"/>
@@ -9424,7 +9428,7 @@
       <c r="H530" s="1"/>
       <c r="I530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" spans="8:8" ht="15.0">
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
       <c r="D531" s="1"/>
@@ -9434,7 +9438,7 @@
       <c r="H531" s="1"/>
       <c r="I531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" spans="8:8" ht="15.0">
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
       <c r="D532" s="1"/>
@@ -9444,7 +9448,7 @@
       <c r="H532" s="1"/>
       <c r="I532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" spans="8:8" ht="15.0">
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
       <c r="D533" s="1"/>
@@ -9454,7 +9458,7 @@
       <c r="H533" s="1"/>
       <c r="I533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" spans="8:8" ht="15.0">
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
       <c r="D534" s="1"/>
@@ -9464,7 +9468,7 @@
       <c r="H534" s="1"/>
       <c r="I534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" spans="8:8" ht="15.0">
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
       <c r="D535" s="1"/>
@@ -9474,7 +9478,7 @@
       <c r="H535" s="1"/>
       <c r="I535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" spans="8:8" ht="15.0">
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
       <c r="D536" s="1"/>
@@ -9484,7 +9488,7 @@
       <c r="H536" s="1"/>
       <c r="I536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" spans="8:8" ht="15.0">
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
       <c r="D537" s="1"/>
@@ -9494,7 +9498,7 @@
       <c r="H537" s="1"/>
       <c r="I537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" spans="8:8" ht="15.0">
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
       <c r="D538" s="1"/>
@@ -9504,7 +9508,7 @@
       <c r="H538" s="1"/>
       <c r="I538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" spans="8:8" ht="15.0">
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
       <c r="D539" s="1"/>
@@ -9514,7 +9518,7 @@
       <c r="H539" s="1"/>
       <c r="I539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" spans="8:8" ht="15.0">
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
       <c r="D540" s="1"/>
@@ -9524,7 +9528,7 @@
       <c r="H540" s="1"/>
       <c r="I540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" spans="8:8" ht="15.0">
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
       <c r="D541" s="1"/>
@@ -9534,7 +9538,7 @@
       <c r="H541" s="1"/>
       <c r="I541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" spans="8:8" ht="15.0">
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
       <c r="D542" s="1"/>
@@ -9544,7 +9548,7 @@
       <c r="H542" s="1"/>
       <c r="I542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" spans="8:8" ht="15.0">
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
       <c r="D543" s="1"/>
@@ -9554,7 +9558,7 @@
       <c r="H543" s="1"/>
       <c r="I543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" spans="8:8" ht="15.0">
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
       <c r="D544" s="1"/>
@@ -9564,7 +9568,7 @@
       <c r="H544" s="1"/>
       <c r="I544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" spans="8:8" ht="15.0">
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
       <c r="D545" s="1"/>
@@ -9574,7 +9578,7 @@
       <c r="H545" s="1"/>
       <c r="I545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" spans="8:8" ht="15.0">
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
       <c r="D546" s="1"/>
@@ -9584,7 +9588,7 @@
       <c r="H546" s="1"/>
       <c r="I546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" spans="8:8" ht="15.0">
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
       <c r="D547" s="1"/>
@@ -9594,7 +9598,7 @@
       <c r="H547" s="1"/>
       <c r="I547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" spans="8:8" ht="15.0">
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
       <c r="D548" s="1"/>
@@ -9604,7 +9608,7 @@
       <c r="H548" s="1"/>
       <c r="I548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" spans="8:8" ht="15.0">
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
       <c r="D549" s="1"/>
@@ -9614,7 +9618,7 @@
       <c r="H549" s="1"/>
       <c r="I549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" spans="8:8" ht="15.0">
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
       <c r="D550" s="1"/>
@@ -9624,7 +9628,7 @@
       <c r="H550" s="1"/>
       <c r="I550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" spans="8:8" ht="15.0">
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
       <c r="D551" s="1"/>
@@ -9634,7 +9638,7 @@
       <c r="H551" s="1"/>
       <c r="I551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" spans="8:8" ht="15.0">
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
       <c r="D552" s="1"/>
@@ -9644,7 +9648,7 @@
       <c r="H552" s="1"/>
       <c r="I552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" spans="8:8" ht="15.0">
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
       <c r="D553" s="1"/>
@@ -9654,7 +9658,7 @@
       <c r="H553" s="1"/>
       <c r="I553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" spans="8:8" ht="15.0">
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
       <c r="D554" s="1"/>
@@ -9664,7 +9668,7 @@
       <c r="H554" s="1"/>
       <c r="I554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" spans="8:8" ht="15.0">
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
       <c r="D555" s="1"/>
@@ -9674,7 +9678,7 @@
       <c r="H555" s="1"/>
       <c r="I555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" spans="8:8" ht="15.0">
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
       <c r="D556" s="1"/>
@@ -9684,7 +9688,7 @@
       <c r="H556" s="1"/>
       <c r="I556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" spans="8:8" ht="15.0">
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
       <c r="D557" s="1"/>
@@ -9694,7 +9698,7 @@
       <c r="H557" s="1"/>
       <c r="I557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" spans="8:8" ht="15.0">
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
       <c r="D558" s="1"/>
@@ -9704,7 +9708,7 @@
       <c r="H558" s="1"/>
       <c r="I558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" spans="8:8" ht="15.0">
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
       <c r="D559" s="1"/>
@@ -9714,7 +9718,7 @@
       <c r="H559" s="1"/>
       <c r="I559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" spans="8:8" ht="15.0">
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
       <c r="D560" s="1"/>
@@ -9724,7 +9728,7 @@
       <c r="H560" s="1"/>
       <c r="I560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" spans="8:8" ht="15.0">
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
       <c r="D561" s="1"/>
@@ -9734,7 +9738,7 @@
       <c r="H561" s="1"/>
       <c r="I561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" spans="8:8" ht="15.0">
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
       <c r="D562" s="1"/>
@@ -9744,7 +9748,7 @@
       <c r="H562" s="1"/>
       <c r="I562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" spans="8:8" ht="15.0">
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
       <c r="D563" s="1"/>
@@ -9754,7 +9758,7 @@
       <c r="H563" s="1"/>
       <c r="I563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" spans="8:8" ht="15.0">
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
       <c r="D564" s="1"/>
@@ -9764,7 +9768,7 @@
       <c r="H564" s="1"/>
       <c r="I564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" spans="8:8" ht="15.0">
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
       <c r="D565" s="1"/>
@@ -9774,7 +9778,7 @@
       <c r="H565" s="1"/>
       <c r="I565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" spans="8:8" ht="15.0">
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
       <c r="D566" s="1"/>
@@ -9784,7 +9788,7 @@
       <c r="H566" s="1"/>
       <c r="I566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" spans="8:8" ht="15.0">
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
       <c r="D567" s="1"/>
@@ -9794,7 +9798,7 @@
       <c r="H567" s="1"/>
       <c r="I567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" spans="8:8" ht="15.0">
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
       <c r="D568" s="1"/>
@@ -9804,7 +9808,7 @@
       <c r="H568" s="1"/>
       <c r="I568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" spans="8:8" ht="15.0">
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
       <c r="D569" s="1"/>
@@ -9814,7 +9818,7 @@
       <c r="H569" s="1"/>
       <c r="I569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" spans="8:8" ht="15.0">
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
       <c r="D570" s="1"/>
@@ -9824,7 +9828,7 @@
       <c r="H570" s="1"/>
       <c r="I570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" spans="8:8" ht="15.0">
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
       <c r="D571" s="1"/>
@@ -9834,7 +9838,7 @@
       <c r="H571" s="1"/>
       <c r="I571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" spans="8:8" ht="15.0">
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
       <c r="D572" s="1"/>
@@ -9844,7 +9848,7 @@
       <c r="H572" s="1"/>
       <c r="I572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" spans="8:8" ht="15.0">
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
       <c r="D573" s="1"/>
@@ -9854,7 +9858,7 @@
       <c r="H573" s="1"/>
       <c r="I573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" spans="8:8" ht="15.0">
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
       <c r="D574" s="1"/>
@@ -9864,7 +9868,7 @@
       <c r="H574" s="1"/>
       <c r="I574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" spans="8:8" ht="15.0">
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
       <c r="D575" s="1"/>
@@ -9874,7 +9878,7 @@
       <c r="H575" s="1"/>
       <c r="I575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" spans="8:8" ht="15.0">
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
       <c r="D576" s="1"/>
@@ -9884,7 +9888,7 @@
       <c r="H576" s="1"/>
       <c r="I576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" spans="8:8" ht="15.0">
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
       <c r="D577" s="1"/>
@@ -9894,7 +9898,7 @@
       <c r="H577" s="1"/>
       <c r="I577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" spans="8:8" ht="15.0">
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
       <c r="D578" s="1"/>
@@ -9904,7 +9908,7 @@
       <c r="H578" s="1"/>
       <c r="I578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" spans="8:8" ht="15.0">
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
       <c r="D579" s="1"/>
@@ -9914,7 +9918,7 @@
       <c r="H579" s="1"/>
       <c r="I579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" spans="8:8" ht="15.0">
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
       <c r="D580" s="1"/>
@@ -9924,7 +9928,7 @@
       <c r="H580" s="1"/>
       <c r="I580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" spans="8:8" ht="15.0">
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
       <c r="D581" s="1"/>
@@ -9934,7 +9938,7 @@
       <c r="H581" s="1"/>
       <c r="I581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" spans="8:8" ht="15.0">
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
       <c r="D582" s="1"/>
@@ -9944,7 +9948,7 @@
       <c r="H582" s="1"/>
       <c r="I582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" spans="8:8" ht="15.0">
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
       <c r="D583" s="1"/>
@@ -9954,7 +9958,7 @@
       <c r="H583" s="1"/>
       <c r="I583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" spans="8:8" ht="15.0">
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
       <c r="D584" s="1"/>
@@ -9964,7 +9968,7 @@
       <c r="H584" s="1"/>
       <c r="I584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" spans="8:8" ht="15.0">
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
       <c r="D585" s="1"/>
@@ -9974,7 +9978,7 @@
       <c r="H585" s="1"/>
       <c r="I585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" spans="8:8" ht="15.0">
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
       <c r="D586" s="1"/>
@@ -9984,7 +9988,7 @@
       <c r="H586" s="1"/>
       <c r="I586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" spans="8:8" ht="15.0">
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
@@ -9994,7 +9998,7 @@
       <c r="H587" s="1"/>
       <c r="I587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" spans="8:8" ht="15.0">
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
       <c r="D588" s="1"/>
@@ -10004,7 +10008,7 @@
       <c r="H588" s="1"/>
       <c r="I588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" spans="8:8" ht="15.0">
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
       <c r="D589" s="1"/>
@@ -10014,7 +10018,7 @@
       <c r="H589" s="1"/>
       <c r="I589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" spans="8:8" ht="15.0">
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
       <c r="D590" s="1"/>
@@ -10024,7 +10028,7 @@
       <c r="H590" s="1"/>
       <c r="I590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" spans="8:8" ht="15.0">
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
       <c r="D591" s="1"/>
@@ -10034,7 +10038,7 @@
       <c r="H591" s="1"/>
       <c r="I591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" spans="8:8" ht="15.0">
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
       <c r="D592" s="1"/>
@@ -10044,7 +10048,7 @@
       <c r="H592" s="1"/>
       <c r="I592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" spans="8:8" ht="15.0">
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
       <c r="D593" s="1"/>
@@ -10054,7 +10058,7 @@
       <c r="H593" s="1"/>
       <c r="I593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" spans="8:8" ht="15.0">
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
       <c r="D594" s="1"/>
@@ -10064,7 +10068,7 @@
       <c r="H594" s="1"/>
       <c r="I594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" spans="8:8" ht="15.0">
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
       <c r="D595" s="1"/>
@@ -10074,7 +10078,7 @@
       <c r="H595" s="1"/>
       <c r="I595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" spans="8:8" ht="15.0">
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
       <c r="D596" s="1"/>
@@ -10084,7 +10088,7 @@
       <c r="H596" s="1"/>
       <c r="I596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" spans="8:8" ht="15.0">
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
       <c r="D597" s="1"/>
@@ -10094,7 +10098,7 @@
       <c r="H597" s="1"/>
       <c r="I597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" spans="8:8" ht="15.0">
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
       <c r="D598" s="1"/>
@@ -10104,7 +10108,7 @@
       <c r="H598" s="1"/>
       <c r="I598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" spans="8:8" ht="15.0">
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
       <c r="D599" s="1"/>
@@ -10114,7 +10118,7 @@
       <c r="H599" s="1"/>
       <c r="I599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" spans="8:8" ht="15.0">
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
       <c r="D600" s="1"/>
@@ -10124,7 +10128,7 @@
       <c r="H600" s="1"/>
       <c r="I600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" spans="8:8" ht="15.0">
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
       <c r="D601" s="1"/>
@@ -10134,7 +10138,7 @@
       <c r="H601" s="1"/>
       <c r="I601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" spans="8:8" ht="15.0">
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
       <c r="D602" s="1"/>
@@ -10144,7 +10148,7 @@
       <c r="H602" s="1"/>
       <c r="I602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" spans="8:8" ht="15.0">
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
       <c r="D603" s="1"/>
@@ -10154,7 +10158,7 @@
       <c r="H603" s="1"/>
       <c r="I603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" spans="8:8" ht="15.0">
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
       <c r="D604" s="1"/>
@@ -10164,7 +10168,7 @@
       <c r="H604" s="1"/>
       <c r="I604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" spans="8:8" ht="15.0">
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
       <c r="D605" s="1"/>
@@ -10174,7 +10178,7 @@
       <c r="H605" s="1"/>
       <c r="I605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" spans="8:8" ht="15.0">
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
       <c r="D606" s="1"/>
@@ -10184,7 +10188,7 @@
       <c r="H606" s="1"/>
       <c r="I606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" spans="8:8" ht="15.0">
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
       <c r="D607" s="1"/>
@@ -10194,7 +10198,7 @@
       <c r="H607" s="1"/>
       <c r="I607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" spans="8:8" ht="15.0">
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
       <c r="D608" s="1"/>
@@ -10204,7 +10208,7 @@
       <c r="H608" s="1"/>
       <c r="I608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" spans="8:8" ht="15.0">
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
       <c r="D609" s="1"/>
@@ -10214,7 +10218,7 @@
       <c r="H609" s="1"/>
       <c r="I609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" spans="8:8" ht="15.0">
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
       <c r="D610" s="1"/>
@@ -10224,7 +10228,7 @@
       <c r="H610" s="1"/>
       <c r="I610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" spans="8:8" ht="15.0">
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
       <c r="D611" s="1"/>
@@ -10234,7 +10238,7 @@
       <c r="H611" s="1"/>
       <c r="I611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" spans="8:8" ht="15.0">
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
       <c r="D612" s="1"/>
@@ -10244,7 +10248,7 @@
       <c r="H612" s="1"/>
       <c r="I612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" spans="8:8" ht="15.0">
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
       <c r="D613" s="1"/>
@@ -10254,7 +10258,7 @@
       <c r="H613" s="1"/>
       <c r="I613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" spans="8:8" ht="15.0">
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
       <c r="D614" s="1"/>
@@ -10264,7 +10268,7 @@
       <c r="H614" s="1"/>
       <c r="I614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" spans="8:8" ht="15.0">
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
       <c r="D615" s="1"/>
@@ -10274,7 +10278,7 @@
       <c r="H615" s="1"/>
       <c r="I615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" spans="8:8" ht="15.0">
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
       <c r="D616" s="1"/>
@@ -10284,7 +10288,7 @@
       <c r="H616" s="1"/>
       <c r="I616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" spans="8:8" ht="15.0">
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
       <c r="D617" s="1"/>
@@ -10294,7 +10298,7 @@
       <c r="H617" s="1"/>
       <c r="I617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" spans="8:8" ht="15.0">
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
       <c r="D618" s="1"/>
@@ -10304,7 +10308,7 @@
       <c r="H618" s="1"/>
       <c r="I618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" spans="8:8" ht="15.0">
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
       <c r="D619" s="1"/>
@@ -10314,7 +10318,7 @@
       <c r="H619" s="1"/>
       <c r="I619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" spans="8:8" ht="15.0">
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
       <c r="D620" s="1"/>
@@ -10324,7 +10328,7 @@
       <c r="H620" s="1"/>
       <c r="I620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" spans="8:8" ht="15.0">
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
       <c r="D621" s="1"/>
@@ -10334,7 +10338,7 @@
       <c r="H621" s="1"/>
       <c r="I621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" spans="8:8" ht="15.0">
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
       <c r="D622" s="1"/>
@@ -10344,7 +10348,7 @@
       <c r="H622" s="1"/>
       <c r="I622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" spans="8:8" ht="15.0">
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
       <c r="D623" s="1"/>
@@ -10354,7 +10358,7 @@
       <c r="H623" s="1"/>
       <c r="I623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" spans="8:8" ht="15.0">
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
       <c r="D624" s="1"/>
@@ -10364,7 +10368,7 @@
       <c r="H624" s="1"/>
       <c r="I624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" spans="8:8" ht="15.0">
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
       <c r="D625" s="1"/>
@@ -10374,7 +10378,7 @@
       <c r="H625" s="1"/>
       <c r="I625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" spans="8:8" ht="15.0">
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
       <c r="D626" s="1"/>
@@ -10384,7 +10388,7 @@
       <c r="H626" s="1"/>
       <c r="I626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" spans="8:8" ht="15.0">
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
       <c r="D627" s="1"/>
@@ -10394,7 +10398,7 @@
       <c r="H627" s="1"/>
       <c r="I627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" spans="8:8" ht="15.0">
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
       <c r="D628" s="1"/>
@@ -10404,7 +10408,7 @@
       <c r="H628" s="1"/>
       <c r="I628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" spans="8:8" ht="15.0">
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
       <c r="D629" s="1"/>
@@ -10414,7 +10418,7 @@
       <c r="H629" s="1"/>
       <c r="I629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" spans="8:8" ht="15.0">
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
       <c r="D630" s="1"/>
@@ -10424,7 +10428,7 @@
       <c r="H630" s="1"/>
       <c r="I630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" spans="8:8" ht="15.0">
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
       <c r="D631" s="1"/>
@@ -10434,7 +10438,7 @@
       <c r="H631" s="1"/>
       <c r="I631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" spans="8:8" ht="15.0">
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
       <c r="D632" s="1"/>
@@ -10444,7 +10448,7 @@
       <c r="H632" s="1"/>
       <c r="I632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" spans="8:8" ht="15.0">
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
       <c r="D633" s="1"/>
@@ -10454,7 +10458,7 @@
       <c r="H633" s="1"/>
       <c r="I633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" spans="8:8" ht="15.0">
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
       <c r="D634" s="1"/>
@@ -10464,7 +10468,7 @@
       <c r="H634" s="1"/>
       <c r="I634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" spans="8:8" ht="15.0">
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
       <c r="D635" s="1"/>
@@ -10474,7 +10478,7 @@
       <c r="H635" s="1"/>
       <c r="I635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" spans="8:8" ht="15.0">
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
       <c r="D636" s="1"/>
@@ -10484,7 +10488,7 @@
       <c r="H636" s="1"/>
       <c r="I636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" spans="8:8" ht="15.0">
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
       <c r="D637" s="1"/>
@@ -10494,7 +10498,7 @@
       <c r="H637" s="1"/>
       <c r="I637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" spans="8:8" ht="15.0">
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
       <c r="D638" s="1"/>
@@ -10504,7 +10508,7 @@
       <c r="H638" s="1"/>
       <c r="I638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" spans="8:8" ht="15.0">
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
       <c r="D639" s="1"/>
@@ -10514,7 +10518,7 @@
       <c r="H639" s="1"/>
       <c r="I639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" spans="8:8" ht="15.0">
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
       <c r="D640" s="1"/>
@@ -10524,7 +10528,7 @@
       <c r="H640" s="1"/>
       <c r="I640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" spans="8:8" ht="15.0">
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
       <c r="D641" s="1"/>
@@ -10534,7 +10538,7 @@
       <c r="H641" s="1"/>
       <c r="I641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" spans="8:8" ht="15.0">
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
       <c r="D642" s="1"/>
@@ -10544,7 +10548,7 @@
       <c r="H642" s="1"/>
       <c r="I642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" spans="8:8" ht="15.0">
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
       <c r="D643" s="1"/>
@@ -10554,7 +10558,7 @@
       <c r="H643" s="1"/>
       <c r="I643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" spans="8:8" ht="15.0">
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
       <c r="D644" s="1"/>
@@ -10564,7 +10568,7 @@
       <c r="H644" s="1"/>
       <c r="I644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" spans="8:8" ht="15.0">
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
       <c r="D645" s="1"/>
@@ -10574,7 +10578,7 @@
       <c r="H645" s="1"/>
       <c r="I645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" spans="8:8" ht="15.0">
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
       <c r="D646" s="1"/>
@@ -10584,7 +10588,7 @@
       <c r="H646" s="1"/>
       <c r="I646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" spans="8:8" ht="15.0">
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
       <c r="D647" s="1"/>
@@ -10594,7 +10598,7 @@
       <c r="H647" s="1"/>
       <c r="I647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" spans="8:8" ht="15.0">
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
       <c r="D648" s="1"/>
@@ -10604,7 +10608,7 @@
       <c r="H648" s="1"/>
       <c r="I648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" spans="8:8" ht="15.0">
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
       <c r="D649" s="1"/>
@@ -10614,7 +10618,7 @@
       <c r="H649" s="1"/>
       <c r="I649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" spans="8:8" ht="15.0">
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
       <c r="D650" s="1"/>
@@ -10624,7 +10628,7 @@
       <c r="H650" s="1"/>
       <c r="I650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" spans="8:8" ht="15.0">
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
       <c r="D651" s="1"/>
@@ -10634,7 +10638,7 @@
       <c r="H651" s="1"/>
       <c r="I651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" spans="8:8" ht="15.0">
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
       <c r="D652" s="1"/>
@@ -10644,7 +10648,7 @@
       <c r="H652" s="1"/>
       <c r="I652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" spans="8:8" ht="15.0">
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
       <c r="D653" s="1"/>
@@ -10654,7 +10658,7 @@
       <c r="H653" s="1"/>
       <c r="I653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" spans="8:8" ht="15.0">
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
       <c r="D654" s="1"/>
@@ -10664,7 +10668,7 @@
       <c r="H654" s="1"/>
       <c r="I654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" spans="8:8" ht="15.0">
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
       <c r="D655" s="1"/>
@@ -10674,7 +10678,7 @@
       <c r="H655" s="1"/>
       <c r="I655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" spans="8:8" ht="15.0">
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
       <c r="D656" s="1"/>
@@ -10684,7 +10688,7 @@
       <c r="H656" s="1"/>
       <c r="I656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" spans="8:8" ht="15.0">
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
       <c r="D657" s="1"/>
@@ -10694,7 +10698,7 @@
       <c r="H657" s="1"/>
       <c r="I657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" spans="8:8" ht="15.0">
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
       <c r="D658" s="1"/>
@@ -10704,7 +10708,7 @@
       <c r="H658" s="1"/>
       <c r="I658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" spans="8:8" ht="15.0">
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
       <c r="D659" s="1"/>
@@ -10714,7 +10718,7 @@
       <c r="H659" s="1"/>
       <c r="I659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" spans="8:8" ht="15.0">
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
       <c r="D660" s="1"/>
@@ -10724,7 +10728,7 @@
       <c r="H660" s="1"/>
       <c r="I660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" spans="8:8" ht="15.0">
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
       <c r="D661" s="1"/>
@@ -10734,7 +10738,7 @@
       <c r="H661" s="1"/>
       <c r="I661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" spans="8:8" ht="15.0">
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
       <c r="D662" s="1"/>
@@ -10744,7 +10748,7 @@
       <c r="H662" s="1"/>
       <c r="I662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" spans="8:8" ht="15.0">
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
       <c r="D663" s="1"/>
@@ -10754,7 +10758,7 @@
       <c r="H663" s="1"/>
       <c r="I663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" spans="8:8" ht="15.0">
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
       <c r="D664" s="1"/>
@@ -10764,7 +10768,7 @@
       <c r="H664" s="1"/>
       <c r="I664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" spans="8:8" ht="15.0">
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
       <c r="D665" s="1"/>
@@ -10774,7 +10778,7 @@
       <c r="H665" s="1"/>
       <c r="I665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" spans="8:8" ht="15.0">
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
       <c r="D666" s="1"/>
@@ -10784,7 +10788,7 @@
       <c r="H666" s="1"/>
       <c r="I666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" spans="8:8" ht="15.0">
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
       <c r="D667" s="1"/>
@@ -10794,7 +10798,7 @@
       <c r="H667" s="1"/>
       <c r="I667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" spans="8:8" ht="15.0">
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
       <c r="D668" s="1"/>
@@ -10804,7 +10808,7 @@
       <c r="H668" s="1"/>
       <c r="I668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" spans="8:8" ht="15.0">
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
       <c r="D669" s="1"/>
@@ -10814,7 +10818,7 @@
       <c r="H669" s="1"/>
       <c r="I669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" spans="8:8" ht="15.0">
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
       <c r="D670" s="1"/>
@@ -10824,7 +10828,7 @@
       <c r="H670" s="1"/>
       <c r="I670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" spans="8:8" ht="15.0">
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
       <c r="D671" s="1"/>
@@ -10834,7 +10838,7 @@
       <c r="H671" s="1"/>
       <c r="I671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" spans="8:8" ht="15.0">
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
       <c r="D672" s="1"/>
@@ -10844,7 +10848,7 @@
       <c r="H672" s="1"/>
       <c r="I672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" spans="8:8" ht="15.0">
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
       <c r="D673" s="1"/>
@@ -10854,7 +10858,7 @@
       <c r="H673" s="1"/>
       <c r="I673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" spans="8:8" ht="15.0">
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
       <c r="D674" s="1"/>
@@ -10864,7 +10868,7 @@
       <c r="H674" s="1"/>
       <c r="I674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" spans="8:8" ht="15.0">
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
       <c r="D675" s="1"/>
@@ -10874,7 +10878,7 @@
       <c r="H675" s="1"/>
       <c r="I675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" spans="8:8" ht="15.0">
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
       <c r="D676" s="1"/>
@@ -10884,7 +10888,7 @@
       <c r="H676" s="1"/>
       <c r="I676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" spans="8:8" ht="15.0">
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
       <c r="D677" s="1"/>
@@ -10894,7 +10898,7 @@
       <c r="H677" s="1"/>
       <c r="I677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" spans="8:8" ht="15.0">
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
       <c r="D678" s="1"/>
@@ -10904,7 +10908,7 @@
       <c r="H678" s="1"/>
       <c r="I678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" spans="8:8" ht="15.0">
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
       <c r="D679" s="1"/>
@@ -10914,7 +10918,7 @@
       <c r="H679" s="1"/>
       <c r="I679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" spans="8:8" ht="15.0">
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
       <c r="D680" s="1"/>
@@ -10924,7 +10928,7 @@
       <c r="H680" s="1"/>
       <c r="I680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" spans="8:8" ht="15.0">
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
       <c r="D681" s="1"/>
@@ -10934,7 +10938,7 @@
       <c r="H681" s="1"/>
       <c r="I681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" spans="8:8" ht="15.0">
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
       <c r="D682" s="1"/>
@@ -10944,7 +10948,7 @@
       <c r="H682" s="1"/>
       <c r="I682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" spans="8:8" ht="15.0">
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
       <c r="D683" s="1"/>
@@ -10954,7 +10958,7 @@
       <c r="H683" s="1"/>
       <c r="I683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" spans="8:8" ht="15.0">
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
       <c r="D684" s="1"/>
@@ -10964,7 +10968,7 @@
       <c r="H684" s="1"/>
       <c r="I684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" spans="8:8" ht="15.0">
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
       <c r="D685" s="1"/>
@@ -10974,7 +10978,7 @@
       <c r="H685" s="1"/>
       <c r="I685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" spans="8:8" ht="15.0">
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
       <c r="D686" s="1"/>
@@ -10984,7 +10988,7 @@
       <c r="H686" s="1"/>
       <c r="I686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" spans="8:8" ht="15.0">
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
       <c r="D687" s="1"/>
@@ -10994,7 +10998,7 @@
       <c r="H687" s="1"/>
       <c r="I687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" spans="8:8" ht="15.0">
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
       <c r="D688" s="1"/>
@@ -11004,7 +11008,7 @@
       <c r="H688" s="1"/>
       <c r="I688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" spans="8:8" ht="15.0">
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
       <c r="D689" s="1"/>
@@ -11014,7 +11018,7 @@
       <c r="H689" s="1"/>
       <c r="I689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" spans="8:8" ht="15.0">
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
       <c r="D690" s="1"/>
@@ -11024,7 +11028,7 @@
       <c r="H690" s="1"/>
       <c r="I690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" spans="8:8" ht="15.0">
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
       <c r="D691" s="1"/>
@@ -11034,7 +11038,7 @@
       <c r="H691" s="1"/>
       <c r="I691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" spans="8:8" ht="15.0">
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
       <c r="D692" s="1"/>
@@ -11044,7 +11048,7 @@
       <c r="H692" s="1"/>
       <c r="I692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" spans="8:8" ht="15.0">
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
       <c r="D693" s="1"/>
@@ -11054,7 +11058,7 @@
       <c r="H693" s="1"/>
       <c r="I693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" spans="8:8" ht="15.0">
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
       <c r="D694" s="1"/>
@@ -11064,7 +11068,7 @@
       <c r="H694" s="1"/>
       <c r="I694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" spans="8:8" ht="15.0">
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
       <c r="D695" s="1"/>
@@ -11074,7 +11078,7 @@
       <c r="H695" s="1"/>
       <c r="I695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" spans="8:8" ht="15.0">
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
       <c r="D696" s="1"/>
@@ -11084,7 +11088,7 @@
       <c r="H696" s="1"/>
       <c r="I696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" spans="8:8" ht="15.0">
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
       <c r="D697" s="1"/>
@@ -11094,7 +11098,7 @@
       <c r="H697" s="1"/>
       <c r="I697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" spans="8:8" ht="15.0">
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
       <c r="D698" s="1"/>
@@ -11104,7 +11108,7 @@
       <c r="H698" s="1"/>
       <c r="I698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" spans="8:8" ht="15.0">
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
       <c r="D699" s="1"/>
@@ -11114,7 +11118,7 @@
       <c r="H699" s="1"/>
       <c r="I699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" spans="8:8" ht="15.0">
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
       <c r="D700" s="1"/>
@@ -11124,7 +11128,7 @@
       <c r="H700" s="1"/>
       <c r="I700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" spans="8:8" ht="15.0">
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
       <c r="D701" s="1"/>
@@ -11134,7 +11138,7 @@
       <c r="H701" s="1"/>
       <c r="I701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" spans="8:8" ht="15.0">
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
       <c r="D702" s="1"/>
@@ -11144,7 +11148,7 @@
       <c r="H702" s="1"/>
       <c r="I702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" spans="8:8" ht="15.0">
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
       <c r="D703" s="1"/>
@@ -11154,7 +11158,7 @@
       <c r="H703" s="1"/>
       <c r="I703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" spans="8:8" ht="15.0">
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
       <c r="D704" s="1"/>
@@ -11164,7 +11168,7 @@
       <c r="H704" s="1"/>
       <c r="I704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" spans="8:8" ht="15.0">
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
       <c r="D705" s="1"/>
@@ -11174,7 +11178,7 @@
       <c r="H705" s="1"/>
       <c r="I705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" spans="8:8" ht="15.0">
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
       <c r="D706" s="1"/>
@@ -11184,7 +11188,7 @@
       <c r="H706" s="1"/>
       <c r="I706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" spans="8:8" ht="15.0">
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
       <c r="D707" s="1"/>
@@ -11194,7 +11198,7 @@
       <c r="H707" s="1"/>
       <c r="I707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" spans="8:8" ht="15.0">
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
       <c r="D708" s="1"/>
@@ -11204,7 +11208,7 @@
       <c r="H708" s="1"/>
       <c r="I708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" spans="8:8" ht="15.0">
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
       <c r="D709" s="1"/>
@@ -11214,7 +11218,7 @@
       <c r="H709" s="1"/>
       <c r="I709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" spans="8:8" ht="15.0">
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
       <c r="D710" s="1"/>
@@ -11224,7 +11228,7 @@
       <c r="H710" s="1"/>
       <c r="I710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" spans="8:8" ht="15.0">
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
       <c r="D711" s="1"/>
@@ -11234,7 +11238,7 @@
       <c r="H711" s="1"/>
       <c r="I711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" spans="8:8" ht="15.0">
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
       <c r="D712" s="1"/>
@@ -11244,7 +11248,7 @@
       <c r="H712" s="1"/>
       <c r="I712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" spans="8:8" ht="15.0">
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
       <c r="D713" s="1"/>
@@ -11254,7 +11258,7 @@
       <c r="H713" s="1"/>
       <c r="I713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" spans="8:8" ht="15.0">
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
       <c r="D714" s="1"/>
@@ -11264,7 +11268,7 @@
       <c r="H714" s="1"/>
       <c r="I714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" spans="8:8" ht="15.0">
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
       <c r="D715" s="1"/>
@@ -11274,7 +11278,7 @@
       <c r="H715" s="1"/>
       <c r="I715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" spans="8:8" ht="15.0">
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
       <c r="D716" s="1"/>
@@ -11284,7 +11288,7 @@
       <c r="H716" s="1"/>
       <c r="I716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" spans="8:8" ht="15.0">
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
       <c r="D717" s="1"/>
@@ -11294,7 +11298,7 @@
       <c r="H717" s="1"/>
       <c r="I717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" spans="8:8" ht="15.0">
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
       <c r="D718" s="1"/>
@@ -11304,7 +11308,7 @@
       <c r="H718" s="1"/>
       <c r="I718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" spans="8:8" ht="15.0">
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
       <c r="D719" s="1"/>
@@ -11314,7 +11318,7 @@
       <c r="H719" s="1"/>
       <c r="I719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" spans="8:8" ht="15.0">
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
       <c r="D720" s="1"/>
@@ -11324,7 +11328,7 @@
       <c r="H720" s="1"/>
       <c r="I720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" spans="8:8" ht="15.0">
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
       <c r="D721" s="1"/>
@@ -11334,7 +11338,7 @@
       <c r="H721" s="1"/>
       <c r="I721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" spans="8:8" ht="15.0">
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
       <c r="D722" s="1"/>
@@ -11344,7 +11348,7 @@
       <c r="H722" s="1"/>
       <c r="I722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" spans="8:8" ht="15.0">
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
       <c r="D723" s="1"/>
@@ -11354,7 +11358,7 @@
       <c r="H723" s="1"/>
       <c r="I723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" spans="8:8" ht="15.0">
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
       <c r="D724" s="1"/>
@@ -11364,7 +11368,7 @@
       <c r="H724" s="1"/>
       <c r="I724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" spans="8:8" ht="15.0">
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
       <c r="D725" s="1"/>
@@ -11374,7 +11378,7 @@
       <c r="H725" s="1"/>
       <c r="I725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" spans="8:8" ht="15.0">
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
       <c r="D726" s="1"/>
@@ -11384,7 +11388,7 @@
       <c r="H726" s="1"/>
       <c r="I726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" spans="8:8" ht="15.0">
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
       <c r="D727" s="1"/>
@@ -11394,7 +11398,7 @@
       <c r="H727" s="1"/>
       <c r="I727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" spans="8:8" ht="15.0">
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
       <c r="D728" s="1"/>
@@ -11404,7 +11408,7 @@
       <c r="H728" s="1"/>
       <c r="I728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" spans="8:8" ht="15.0">
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
       <c r="D729" s="1"/>
@@ -11414,7 +11418,7 @@
       <c r="H729" s="1"/>
       <c r="I729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" spans="8:8" ht="15.0">
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
       <c r="D730" s="1"/>
@@ -11424,7 +11428,7 @@
       <c r="H730" s="1"/>
       <c r="I730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" spans="8:8" ht="15.0">
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
       <c r="D731" s="1"/>
@@ -11434,7 +11438,7 @@
       <c r="H731" s="1"/>
       <c r="I731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" spans="8:8" ht="15.0">
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
       <c r="D732" s="1"/>
@@ -11444,7 +11448,7 @@
       <c r="H732" s="1"/>
       <c r="I732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" spans="8:8" ht="15.0">
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
       <c r="D733" s="1"/>
@@ -11454,7 +11458,7 @@
       <c r="H733" s="1"/>
       <c r="I733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" spans="8:8" ht="15.0">
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
       <c r="D734" s="1"/>
@@ -11464,7 +11468,7 @@
       <c r="H734" s="1"/>
       <c r="I734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" spans="8:8" ht="15.0">
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
       <c r="D735" s="1"/>
@@ -11474,7 +11478,7 @@
       <c r="H735" s="1"/>
       <c r="I735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" spans="8:8" ht="15.0">
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
       <c r="D736" s="1"/>
@@ -11484,7 +11488,7 @@
       <c r="H736" s="1"/>
       <c r="I736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" spans="8:8" ht="15.0">
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
       <c r="D737" s="1"/>
@@ -11494,7 +11498,7 @@
       <c r="H737" s="1"/>
       <c r="I737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" spans="8:8" ht="15.0">
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
       <c r="D738" s="1"/>
@@ -11504,7 +11508,7 @@
       <c r="H738" s="1"/>
       <c r="I738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" spans="8:8" ht="15.0">
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
       <c r="D739" s="1"/>
@@ -11514,7 +11518,7 @@
       <c r="H739" s="1"/>
       <c r="I739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" spans="8:8" ht="15.0">
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
       <c r="D740" s="1"/>
@@ -11524,7 +11528,7 @@
       <c r="H740" s="1"/>
       <c r="I740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" spans="8:8" ht="15.0">
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
       <c r="D741" s="1"/>
@@ -11534,7 +11538,7 @@
       <c r="H741" s="1"/>
       <c r="I741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" spans="8:8" ht="15.0">
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
       <c r="D742" s="1"/>
@@ -11544,7 +11548,7 @@
       <c r="H742" s="1"/>
       <c r="I742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" spans="8:8" ht="15.0">
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
       <c r="D743" s="1"/>
@@ -11554,7 +11558,7 @@
       <c r="H743" s="1"/>
       <c r="I743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" spans="8:8" ht="15.0">
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
       <c r="D744" s="1"/>
@@ -11564,7 +11568,7 @@
       <c r="H744" s="1"/>
       <c r="I744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" spans="8:8" ht="15.0">
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
       <c r="D745" s="1"/>
@@ -11574,7 +11578,7 @@
       <c r="H745" s="1"/>
       <c r="I745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" spans="8:8" ht="15.0">
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
       <c r="D746" s="1"/>
@@ -11584,7 +11588,7 @@
       <c r="H746" s="1"/>
       <c r="I746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" spans="8:8" ht="15.0">
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
       <c r="D747" s="1"/>
@@ -11594,7 +11598,7 @@
       <c r="H747" s="1"/>
       <c r="I747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" spans="8:8" ht="15.0">
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
       <c r="D748" s="1"/>
@@ -11604,7 +11608,7 @@
       <c r="H748" s="1"/>
       <c r="I748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" spans="8:8" ht="15.0">
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
       <c r="D749" s="1"/>
@@ -11614,7 +11618,7 @@
       <c r="H749" s="1"/>
       <c r="I749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" spans="8:8" ht="15.0">
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
       <c r="D750" s="1"/>
@@ -11624,7 +11628,7 @@
       <c r="H750" s="1"/>
       <c r="I750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" spans="8:8" ht="15.0">
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
       <c r="D751" s="1"/>
@@ -11634,7 +11638,7 @@
       <c r="H751" s="1"/>
       <c r="I751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" spans="8:8" ht="15.0">
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
       <c r="D752" s="1"/>
@@ -11644,7 +11648,7 @@
       <c r="H752" s="1"/>
       <c r="I752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" spans="8:8" ht="15.0">
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
       <c r="D753" s="1"/>
@@ -11654,7 +11658,7 @@
       <c r="H753" s="1"/>
       <c r="I753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" spans="8:8" ht="15.0">
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
       <c r="D754" s="1"/>
@@ -11664,7 +11668,7 @@
       <c r="H754" s="1"/>
       <c r="I754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" spans="8:8" ht="15.0">
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
       <c r="D755" s="1"/>
@@ -11674,7 +11678,7 @@
       <c r="H755" s="1"/>
       <c r="I755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" spans="8:8" ht="15.0">
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
       <c r="D756" s="1"/>
@@ -11684,7 +11688,7 @@
       <c r="H756" s="1"/>
       <c r="I756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" spans="8:8" ht="15.0">
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
       <c r="D757" s="1"/>
@@ -11694,7 +11698,7 @@
       <c r="H757" s="1"/>
       <c r="I757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" spans="8:8" ht="15.0">
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
       <c r="D758" s="1"/>
@@ -11704,7 +11708,7 @@
       <c r="H758" s="1"/>
       <c r="I758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" spans="8:8" ht="15.0">
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
       <c r="D759" s="1"/>
@@ -11714,7 +11718,7 @@
       <c r="H759" s="1"/>
       <c r="I759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" spans="8:8" ht="15.0">
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
       <c r="D760" s="1"/>
@@ -11724,7 +11728,7 @@
       <c r="H760" s="1"/>
       <c r="I760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" spans="8:8" ht="15.0">
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
       <c r="D761" s="1"/>
@@ -11734,7 +11738,7 @@
       <c r="H761" s="1"/>
       <c r="I761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" spans="8:8" ht="15.0">
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
       <c r="D762" s="1"/>
@@ -11744,7 +11748,7 @@
       <c r="H762" s="1"/>
       <c r="I762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" spans="8:8" ht="15.0">
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
       <c r="D763" s="1"/>
@@ -11754,7 +11758,7 @@
       <c r="H763" s="1"/>
       <c r="I763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" spans="8:8" ht="15.0">
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
       <c r="D764" s="1"/>
@@ -11764,7 +11768,7 @@
       <c r="H764" s="1"/>
       <c r="I764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" spans="8:8" ht="15.0">
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
       <c r="D765" s="1"/>
@@ -11774,7 +11778,7 @@
       <c r="H765" s="1"/>
       <c r="I765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" spans="8:8" ht="15.0">
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
       <c r="D766" s="1"/>
@@ -11784,7 +11788,7 @@
       <c r="H766" s="1"/>
       <c r="I766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" spans="8:8" ht="15.0">
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
       <c r="D767" s="1"/>
@@ -11794,7 +11798,7 @@
       <c r="H767" s="1"/>
       <c r="I767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" spans="8:8" ht="15.0">
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
       <c r="D768" s="1"/>
@@ -11804,7 +11808,7 @@
       <c r="H768" s="1"/>
       <c r="I768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" spans="8:8" ht="15.0">
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
       <c r="D769" s="1"/>
@@ -11814,7 +11818,7 @@
       <c r="H769" s="1"/>
       <c r="I769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" spans="8:8" ht="15.0">
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
       <c r="D770" s="1"/>
@@ -11824,7 +11828,7 @@
       <c r="H770" s="1"/>
       <c r="I770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" spans="8:8" ht="15.0">
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
       <c r="D771" s="1"/>
@@ -11834,7 +11838,7 @@
       <c r="H771" s="1"/>
       <c r="I771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" spans="8:8" ht="15.0">
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
       <c r="D772" s="1"/>
@@ -11844,7 +11848,7 @@
       <c r="H772" s="1"/>
       <c r="I772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" spans="8:8" ht="15.0">
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
       <c r="D773" s="1"/>
@@ -11854,7 +11858,7 @@
       <c r="H773" s="1"/>
       <c r="I773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" spans="8:8" ht="15.0">
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
       <c r="D774" s="1"/>
@@ -11864,7 +11868,7 @@
       <c r="H774" s="1"/>
       <c r="I774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" spans="8:8" ht="15.0">
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
       <c r="D775" s="1"/>
@@ -11874,7 +11878,7 @@
       <c r="H775" s="1"/>
       <c r="I775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" spans="8:8" ht="15.0">
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
       <c r="D776" s="1"/>
@@ -11884,7 +11888,7 @@
       <c r="H776" s="1"/>
       <c r="I776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" spans="8:8" ht="15.0">
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
       <c r="D777" s="1"/>
@@ -11894,7 +11898,7 @@
       <c r="H777" s="1"/>
       <c r="I777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" spans="8:8" ht="15.0">
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
       <c r="D778" s="1"/>
@@ -11904,7 +11908,7 @@
       <c r="H778" s="1"/>
       <c r="I778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" spans="8:8" ht="15.0">
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
       <c r="D779" s="1"/>
@@ -11914,7 +11918,7 @@
       <c r="H779" s="1"/>
       <c r="I779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" spans="8:8" ht="15.0">
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
       <c r="D780" s="1"/>
@@ -11924,7 +11928,7 @@
       <c r="H780" s="1"/>
       <c r="I780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" spans="8:8" ht="15.0">
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
       <c r="D781" s="1"/>
@@ -11934,7 +11938,7 @@
       <c r="H781" s="1"/>
       <c r="I781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" spans="8:8" ht="15.0">
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
       <c r="D782" s="1"/>
@@ -11944,7 +11948,7 @@
       <c r="H782" s="1"/>
       <c r="I782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" spans="8:8" ht="15.0">
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
       <c r="D783" s="1"/>
@@ -11954,7 +11958,7 @@
       <c r="H783" s="1"/>
       <c r="I783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" spans="8:8" ht="15.0">
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
       <c r="D784" s="1"/>
@@ -11964,7 +11968,7 @@
       <c r="H784" s="1"/>
       <c r="I784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" spans="8:8" ht="15.0">
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
       <c r="D785" s="1"/>
@@ -11974,7 +11978,7 @@
       <c r="H785" s="1"/>
       <c r="I785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" spans="8:8" ht="15.0">
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
       <c r="D786" s="1"/>
@@ -11984,7 +11988,7 @@
       <c r="H786" s="1"/>
       <c r="I786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" spans="8:8" ht="15.0">
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
       <c r="D787" s="1"/>
@@ -11994,7 +11998,7 @@
       <c r="H787" s="1"/>
       <c r="I787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" spans="8:8" ht="15.0">
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
       <c r="D788" s="1"/>
@@ -12004,7 +12008,7 @@
       <c r="H788" s="1"/>
       <c r="I788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" spans="8:8" ht="15.0">
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
       <c r="D789" s="1"/>
@@ -12014,7 +12018,7 @@
       <c r="H789" s="1"/>
       <c r="I789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" spans="8:8" ht="15.0">
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
       <c r="D790" s="1"/>
@@ -12024,7 +12028,7 @@
       <c r="H790" s="1"/>
       <c r="I790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" spans="8:8" ht="15.0">
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
       <c r="D791" s="1"/>
@@ -12034,7 +12038,7 @@
       <c r="H791" s="1"/>
       <c r="I791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" spans="8:8" ht="15.0">
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
       <c r="D792" s="1"/>
@@ -12044,7 +12048,7 @@
       <c r="H792" s="1"/>
       <c r="I792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" spans="8:8" ht="15.0">
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
       <c r="D793" s="1"/>
@@ -12054,7 +12058,7 @@
       <c r="H793" s="1"/>
       <c r="I793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" spans="8:8" ht="15.0">
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
       <c r="D794" s="1"/>
@@ -12064,7 +12068,7 @@
       <c r="H794" s="1"/>
       <c r="I794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" spans="8:8" ht="15.0">
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
       <c r="D795" s="1"/>
@@ -12074,7 +12078,7 @@
       <c r="H795" s="1"/>
       <c r="I795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" spans="8:8" ht="15.0">
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
       <c r="D796" s="1"/>
@@ -12084,7 +12088,7 @@
       <c r="H796" s="1"/>
       <c r="I796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" spans="8:8" ht="15.0">
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
       <c r="D797" s="1"/>
@@ -12094,7 +12098,7 @@
       <c r="H797" s="1"/>
       <c r="I797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" spans="8:8" ht="15.0">
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
       <c r="D798" s="1"/>
@@ -12104,7 +12108,7 @@
       <c r="H798" s="1"/>
       <c r="I798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" spans="8:8" ht="15.0">
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
       <c r="D799" s="1"/>
@@ -12114,7 +12118,7 @@
       <c r="H799" s="1"/>
       <c r="I799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" spans="8:8" ht="15.0">
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
       <c r="D800" s="1"/>
@@ -12124,7 +12128,7 @@
       <c r="H800" s="1"/>
       <c r="I800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" spans="8:8" ht="15.0">
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
       <c r="D801" s="1"/>
@@ -12134,7 +12138,7 @@
       <c r="H801" s="1"/>
       <c r="I801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" spans="8:8" ht="15.0">
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
       <c r="D802" s="1"/>
@@ -12144,7 +12148,7 @@
       <c r="H802" s="1"/>
       <c r="I802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" spans="8:8" ht="15.0">
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
       <c r="D803" s="1"/>
@@ -12154,7 +12158,7 @@
       <c r="H803" s="1"/>
       <c r="I803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" spans="8:8" ht="15.0">
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
       <c r="D804" s="1"/>
@@ -12164,7 +12168,7 @@
       <c r="H804" s="1"/>
       <c r="I804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" spans="8:8" ht="15.0">
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
       <c r="D805" s="1"/>
@@ -12174,7 +12178,7 @@
       <c r="H805" s="1"/>
       <c r="I805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" spans="8:8" ht="15.0">
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
       <c r="D806" s="1"/>
@@ -12184,7 +12188,7 @@
       <c r="H806" s="1"/>
       <c r="I806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" spans="8:8" ht="15.0">
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
       <c r="D807" s="1"/>
@@ -12194,7 +12198,7 @@
       <c r="H807" s="1"/>
       <c r="I807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" spans="8:8" ht="15.0">
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
       <c r="D808" s="1"/>
@@ -12204,7 +12208,7 @@
       <c r="H808" s="1"/>
       <c r="I808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" spans="8:8" ht="15.0">
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
       <c r="D809" s="1"/>
@@ -12214,7 +12218,7 @@
       <c r="H809" s="1"/>
       <c r="I809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" spans="8:8" ht="15.0">
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
       <c r="D810" s="1"/>
@@ -12224,7 +12228,7 @@
       <c r="H810" s="1"/>
       <c r="I810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" spans="8:8" ht="15.0">
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
       <c r="D811" s="1"/>
@@ -12234,7 +12238,7 @@
       <c r="H811" s="1"/>
       <c r="I811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" spans="8:8" ht="15.0">
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
       <c r="D812" s="1"/>
@@ -12244,7 +12248,7 @@
       <c r="H812" s="1"/>
       <c r="I812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" spans="8:8" ht="15.0">
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
       <c r="D813" s="1"/>
@@ -12254,7 +12258,7 @@
       <c r="H813" s="1"/>
       <c r="I813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" spans="8:8" ht="15.0">
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
       <c r="D814" s="1"/>
@@ -12264,7 +12268,7 @@
       <c r="H814" s="1"/>
       <c r="I814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" spans="8:8" ht="15.0">
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
       <c r="D815" s="1"/>
@@ -12274,7 +12278,7 @@
       <c r="H815" s="1"/>
       <c r="I815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" spans="8:8" ht="15.0">
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
       <c r="D816" s="1"/>
@@ -12284,7 +12288,7 @@
       <c r="H816" s="1"/>
       <c r="I816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" spans="8:8" ht="15.0">
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
       <c r="D817" s="1"/>
@@ -12294,7 +12298,7 @@
       <c r="H817" s="1"/>
       <c r="I817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" spans="8:8" ht="15.0">
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
       <c r="D818" s="1"/>
@@ -12304,7 +12308,7 @@
       <c r="H818" s="1"/>
       <c r="I818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" spans="8:8" ht="15.0">
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
       <c r="D819" s="1"/>
@@ -12314,7 +12318,7 @@
       <c r="H819" s="1"/>
       <c r="I819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" spans="8:8" ht="15.0">
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
       <c r="D820" s="1"/>
@@ -12324,7 +12328,7 @@
       <c r="H820" s="1"/>
       <c r="I820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" spans="8:8" ht="15.0">
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
       <c r="D821" s="1"/>
@@ -12334,7 +12338,7 @@
       <c r="H821" s="1"/>
       <c r="I821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" spans="8:8" ht="15.0">
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
       <c r="D822" s="1"/>
@@ -12344,7 +12348,7 @@
       <c r="H822" s="1"/>
       <c r="I822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" spans="8:8" ht="15.0">
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
       <c r="D823" s="1"/>
@@ -12354,7 +12358,7 @@
       <c r="H823" s="1"/>
       <c r="I823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" spans="8:8" ht="15.0">
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
       <c r="D824" s="1"/>
@@ -12364,7 +12368,7 @@
       <c r="H824" s="1"/>
       <c r="I824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" spans="8:8" ht="15.0">
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
       <c r="D825" s="1"/>
@@ -12374,7 +12378,7 @@
       <c r="H825" s="1"/>
       <c r="I825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" spans="8:8" ht="15.0">
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
       <c r="D826" s="1"/>
@@ -12384,7 +12388,7 @@
       <c r="H826" s="1"/>
       <c r="I826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" spans="8:8" ht="15.0">
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
       <c r="D827" s="1"/>
@@ -12394,7 +12398,7 @@
       <c r="H827" s="1"/>
       <c r="I827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" spans="8:8" ht="15.0">
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
       <c r="D828" s="1"/>
@@ -12404,7 +12408,7 @@
       <c r="H828" s="1"/>
       <c r="I828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" spans="8:8" ht="15.0">
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
       <c r="D829" s="1"/>
@@ -12414,7 +12418,7 @@
       <c r="H829" s="1"/>
       <c r="I829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" spans="8:8" ht="15.0">
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
       <c r="D830" s="1"/>
@@ -12424,7 +12428,7 @@
       <c r="H830" s="1"/>
       <c r="I830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" spans="8:8" ht="15.0">
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
       <c r="D831" s="1"/>
@@ -12434,7 +12438,7 @@
       <c r="H831" s="1"/>
       <c r="I831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" spans="8:8" ht="15.0">
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
       <c r="D832" s="1"/>
@@ -12444,7 +12448,7 @@
       <c r="H832" s="1"/>
       <c r="I832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" spans="8:8" ht="15.0">
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
       <c r="D833" s="1"/>
@@ -12454,7 +12458,7 @@
       <c r="H833" s="1"/>
       <c r="I833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" spans="8:8" ht="15.0">
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
       <c r="D834" s="1"/>
@@ -12464,7 +12468,7 @@
       <c r="H834" s="1"/>
       <c r="I834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" spans="8:8" ht="15.0">
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
       <c r="D835" s="1"/>
@@ -12474,7 +12478,7 @@
       <c r="H835" s="1"/>
       <c r="I835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" spans="8:8" ht="15.0">
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
       <c r="D836" s="1"/>
@@ -12484,7 +12488,7 @@
       <c r="H836" s="1"/>
       <c r="I836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" spans="8:8" ht="15.0">
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
       <c r="D837" s="1"/>
@@ -12494,7 +12498,7 @@
       <c r="H837" s="1"/>
       <c r="I837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" spans="8:8" ht="15.0">
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
       <c r="D838" s="1"/>
@@ -12504,7 +12508,7 @@
       <c r="H838" s="1"/>
       <c r="I838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" spans="8:8" ht="15.0">
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
       <c r="D839" s="1"/>
@@ -12514,7 +12518,7 @@
       <c r="H839" s="1"/>
       <c r="I839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" spans="8:8" ht="15.0">
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
       <c r="D840" s="1"/>
@@ -12524,7 +12528,7 @@
       <c r="H840" s="1"/>
       <c r="I840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" spans="8:8" ht="15.0">
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
       <c r="D841" s="1"/>
@@ -12534,7 +12538,7 @@
       <c r="H841" s="1"/>
       <c r="I841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" spans="8:8" ht="15.0">
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
       <c r="D842" s="1"/>
@@ -12544,7 +12548,7 @@
       <c r="H842" s="1"/>
       <c r="I842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" spans="8:8" ht="15.0">
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
       <c r="D843" s="1"/>
@@ -12554,7 +12558,7 @@
       <c r="H843" s="1"/>
       <c r="I843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" spans="8:8" ht="15.0">
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
       <c r="D844" s="1"/>
@@ -12564,7 +12568,7 @@
       <c r="H844" s="1"/>
       <c r="I844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" spans="8:8" ht="15.0">
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
       <c r="D845" s="1"/>
@@ -12574,7 +12578,7 @@
       <c r="H845" s="1"/>
       <c r="I845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" spans="8:8" ht="15.0">
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
       <c r="D846" s="1"/>
@@ -12584,7 +12588,7 @@
       <c r="H846" s="1"/>
       <c r="I846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" spans="8:8" ht="15.0">
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
       <c r="D847" s="1"/>
@@ -12594,7 +12598,7 @@
       <c r="H847" s="1"/>
       <c r="I847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" spans="8:8" ht="15.0">
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
       <c r="D848" s="1"/>
@@ -12604,7 +12608,7 @@
       <c r="H848" s="1"/>
       <c r="I848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" spans="8:8" ht="15.0">
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
       <c r="D849" s="1"/>
@@ -12614,7 +12618,7 @@
       <c r="H849" s="1"/>
       <c r="I849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" spans="8:8" ht="15.0">
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
       <c r="D850" s="1"/>
@@ -12624,7 +12628,7 @@
       <c r="H850" s="1"/>
       <c r="I850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" spans="8:8" ht="15.0">
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
       <c r="D851" s="1"/>
@@ -12634,7 +12638,7 @@
       <c r="H851" s="1"/>
       <c r="I851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" spans="8:8" ht="15.0">
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
       <c r="D852" s="1"/>
@@ -12644,7 +12648,7 @@
       <c r="H852" s="1"/>
       <c r="I852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" spans="8:8" ht="15.0">
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
       <c r="D853" s="1"/>
@@ -12654,7 +12658,7 @@
       <c r="H853" s="1"/>
       <c r="I853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" spans="8:8" ht="15.0">
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
       <c r="D854" s="1"/>
@@ -12664,7 +12668,7 @@
       <c r="H854" s="1"/>
       <c r="I854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" spans="8:8" ht="15.0">
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
       <c r="D855" s="1"/>
@@ -12674,7 +12678,7 @@
       <c r="H855" s="1"/>
       <c r="I855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" spans="8:8" ht="15.0">
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
       <c r="D856" s="1"/>
@@ -12684,7 +12688,7 @@
       <c r="H856" s="1"/>
       <c r="I856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" spans="8:8" ht="15.0">
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
       <c r="D857" s="1"/>
@@ -12694,7 +12698,7 @@
       <c r="H857" s="1"/>
       <c r="I857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" spans="8:8" ht="15.0">
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
       <c r="D858" s="1"/>
@@ -12704,7 +12708,7 @@
       <c r="H858" s="1"/>
       <c r="I858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" spans="8:8" ht="15.0">
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
       <c r="D859" s="1"/>
@@ -12714,7 +12718,7 @@
       <c r="H859" s="1"/>
       <c r="I859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" spans="8:8" ht="15.0">
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
       <c r="D860" s="1"/>
@@ -12724,7 +12728,7 @@
       <c r="H860" s="1"/>
       <c r="I860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" spans="8:8" ht="15.0">
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
       <c r="D861" s="1"/>
@@ -12734,7 +12738,7 @@
       <c r="H861" s="1"/>
       <c r="I861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" spans="8:8" ht="15.0">
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
       <c r="D862" s="1"/>
@@ -12744,7 +12748,7 @@
       <c r="H862" s="1"/>
       <c r="I862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" spans="8:8" ht="15.0">
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
       <c r="D863" s="1"/>
@@ -12754,7 +12758,7 @@
       <c r="H863" s="1"/>
       <c r="I863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" spans="8:8" ht="15.0">
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
       <c r="D864" s="1"/>
@@ -12764,7 +12768,7 @@
       <c r="H864" s="1"/>
       <c r="I864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" spans="8:8" ht="15.0">
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
       <c r="D865" s="1"/>
@@ -12774,7 +12778,7 @@
       <c r="H865" s="1"/>
       <c r="I865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" spans="8:8" ht="15.0">
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
       <c r="D866" s="1"/>
@@ -12784,7 +12788,7 @@
       <c r="H866" s="1"/>
       <c r="I866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" spans="8:8" ht="15.0">
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
       <c r="D867" s="1"/>
@@ -12794,7 +12798,7 @@
       <c r="H867" s="1"/>
       <c r="I867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" spans="8:8" ht="15.0">
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
       <c r="D868" s="1"/>
@@ -12804,7 +12808,7 @@
       <c r="H868" s="1"/>
       <c r="I868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" spans="8:8" ht="15.0">
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
       <c r="D869" s="1"/>
@@ -12814,7 +12818,7 @@
       <c r="H869" s="1"/>
       <c r="I869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" spans="8:8" ht="15.0">
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
       <c r="D870" s="1"/>
@@ -12824,7 +12828,7 @@
       <c r="H870" s="1"/>
       <c r="I870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" spans="8:8" ht="15.0">
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
       <c r="D871" s="1"/>
@@ -12834,7 +12838,7 @@
       <c r="H871" s="1"/>
       <c r="I871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" spans="8:8" ht="15.0">
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
       <c r="D872" s="1"/>
@@ -12844,7 +12848,7 @@
       <c r="H872" s="1"/>
       <c r="I872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" spans="8:8" ht="15.0">
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
       <c r="D873" s="1"/>
@@ -12854,7 +12858,7 @@
       <c r="H873" s="1"/>
       <c r="I873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" spans="8:8" ht="15.0">
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
       <c r="D874" s="1"/>
@@ -12864,7 +12868,7 @@
       <c r="H874" s="1"/>
       <c r="I874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" spans="8:8" ht="15.0">
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
       <c r="D875" s="1"/>
@@ -12874,7 +12878,7 @@
       <c r="H875" s="1"/>
       <c r="I875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" spans="8:8" ht="15.0">
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
       <c r="D876" s="1"/>
@@ -12884,7 +12888,7 @@
       <c r="H876" s="1"/>
       <c r="I876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" spans="8:8" ht="15.0">
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
       <c r="D877" s="1"/>
@@ -12894,7 +12898,7 @@
       <c r="H877" s="1"/>
       <c r="I877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" spans="8:8" ht="15.0">
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
       <c r="D878" s="1"/>
@@ -12904,7 +12908,7 @@
       <c r="H878" s="1"/>
       <c r="I878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" spans="8:8" ht="15.0">
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
       <c r="D879" s="1"/>
@@ -12914,7 +12918,7 @@
       <c r="H879" s="1"/>
       <c r="I879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" spans="8:8" ht="15.0">
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
       <c r="D880" s="1"/>
@@ -12924,7 +12928,7 @@
       <c r="H880" s="1"/>
       <c r="I880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" spans="8:8" ht="15.0">
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
       <c r="D881" s="1"/>
@@ -12934,7 +12938,7 @@
       <c r="H881" s="1"/>
       <c r="I881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" spans="8:8" ht="15.0">
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
       <c r="D882" s="1"/>
@@ -12944,7 +12948,7 @@
       <c r="H882" s="1"/>
       <c r="I882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" spans="8:8" ht="15.0">
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
       <c r="D883" s="1"/>
@@ -12954,7 +12958,7 @@
       <c r="H883" s="1"/>
       <c r="I883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" spans="8:8" ht="15.0">
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
       <c r="D884" s="1"/>
@@ -12964,7 +12968,7 @@
       <c r="H884" s="1"/>
       <c r="I884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" spans="8:8" ht="15.0">
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
       <c r="D885" s="1"/>
@@ -12974,7 +12978,7 @@
       <c r="H885" s="1"/>
       <c r="I885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" spans="8:8" ht="15.0">
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
       <c r="D886" s="1"/>
@@ -12984,7 +12988,7 @@
       <c r="H886" s="1"/>
       <c r="I886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" spans="8:8" ht="15.0">
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
       <c r="D887" s="1"/>
@@ -12994,7 +12998,7 @@
       <c r="H887" s="1"/>
       <c r="I887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" spans="8:8" ht="15.0">
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
       <c r="D888" s="1"/>
@@ -13004,7 +13008,7 @@
       <c r="H888" s="1"/>
       <c r="I888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" spans="8:8" ht="15.0">
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
       <c r="D889" s="1"/>
@@ -13014,7 +13018,7 @@
       <c r="H889" s="1"/>
       <c r="I889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" spans="8:8" ht="15.0">
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
       <c r="D890" s="1"/>
@@ -13024,7 +13028,7 @@
       <c r="H890" s="1"/>
       <c r="I890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" spans="8:8" ht="15.0">
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
       <c r="D891" s="1"/>
@@ -13034,7 +13038,7 @@
       <c r="H891" s="1"/>
       <c r="I891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" spans="8:8" ht="15.0">
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
       <c r="D892" s="1"/>
@@ -13044,7 +13048,7 @@
       <c r="H892" s="1"/>
       <c r="I892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" spans="8:8" ht="15.0">
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
       <c r="D893" s="1"/>
@@ -13054,7 +13058,7 @@
       <c r="H893" s="1"/>
       <c r="I893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" spans="8:8" ht="15.0">
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
       <c r="D894" s="1"/>
@@ -13064,7 +13068,7 @@
       <c r="H894" s="1"/>
       <c r="I894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" spans="8:8" ht="15.0">
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
       <c r="D895" s="1"/>
@@ -13074,7 +13078,7 @@
       <c r="H895" s="1"/>
       <c r="I895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" spans="8:8" ht="15.0">
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
       <c r="D896" s="1"/>
@@ -13084,7 +13088,7 @@
       <c r="H896" s="1"/>
       <c r="I896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" spans="8:8" ht="15.0">
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
       <c r="D897" s="1"/>
@@ -13094,7 +13098,7 @@
       <c r="H897" s="1"/>
       <c r="I897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" spans="8:8" ht="15.0">
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
       <c r="D898" s="1"/>
@@ -13104,7 +13108,7 @@
       <c r="H898" s="1"/>
       <c r="I898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" spans="8:8" ht="15.0">
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
       <c r="D899" s="1"/>
@@ -13114,7 +13118,7 @@
       <c r="H899" s="1"/>
       <c r="I899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" spans="8:8" ht="15.0">
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
       <c r="D900" s="1"/>
@@ -13124,7 +13128,7 @@
       <c r="H900" s="1"/>
       <c r="I900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" spans="8:8" ht="15.0">
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
       <c r="D901" s="1"/>
@@ -13134,7 +13138,7 @@
       <c r="H901" s="1"/>
       <c r="I901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" spans="8:8" ht="15.0">
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
       <c r="D902" s="1"/>
@@ -13144,7 +13148,7 @@
       <c r="H902" s="1"/>
       <c r="I902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" spans="8:8" ht="15.0">
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
       <c r="D903" s="1"/>
@@ -13154,7 +13158,7 @@
       <c r="H903" s="1"/>
       <c r="I903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" spans="8:8" ht="15.0">
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
       <c r="D904" s="1"/>
@@ -13164,7 +13168,7 @@
       <c r="H904" s="1"/>
       <c r="I904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" spans="8:8" ht="15.0">
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
       <c r="D905" s="1"/>
@@ -13174,7 +13178,7 @@
       <c r="H905" s="1"/>
       <c r="I905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" spans="8:8" ht="15.0">
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
       <c r="D906" s="1"/>
@@ -13184,7 +13188,7 @@
       <c r="H906" s="1"/>
       <c r="I906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" spans="8:8" ht="15.0">
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
       <c r="D907" s="1"/>
@@ -13194,7 +13198,7 @@
       <c r="H907" s="1"/>
       <c r="I907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" spans="8:8" ht="15.0">
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
       <c r="D908" s="1"/>
@@ -13204,7 +13208,7 @@
       <c r="H908" s="1"/>
       <c r="I908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" spans="8:8" ht="15.0">
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
       <c r="D909" s="1"/>
@@ -13214,7 +13218,7 @@
       <c r="H909" s="1"/>
       <c r="I909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" spans="8:8" ht="15.0">
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
       <c r="D910" s="1"/>
@@ -13224,7 +13228,7 @@
       <c r="H910" s="1"/>
       <c r="I910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" spans="8:8" ht="15.0">
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
       <c r="D911" s="1"/>
@@ -13234,7 +13238,7 @@
       <c r="H911" s="1"/>
       <c r="I911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" spans="8:8" ht="15.0">
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
       <c r="D912" s="1"/>
@@ -13244,7 +13248,7 @@
       <c r="H912" s="1"/>
       <c r="I912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" spans="8:8" ht="15.0">
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
       <c r="D913" s="1"/>
@@ -13254,7 +13258,7 @@
       <c r="H913" s="1"/>
       <c r="I913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" spans="8:8" ht="15.0">
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
       <c r="D914" s="1"/>
@@ -13264,7 +13268,7 @@
       <c r="H914" s="1"/>
       <c r="I914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" spans="8:8" ht="15.0">
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
       <c r="D915" s="1"/>
@@ -13274,7 +13278,7 @@
       <c r="H915" s="1"/>
       <c r="I915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" spans="8:8" ht="15.0">
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
       <c r="D916" s="1"/>
@@ -13284,7 +13288,7 @@
       <c r="H916" s="1"/>
       <c r="I916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" spans="8:8" ht="15.0">
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
       <c r="D917" s="1"/>
@@ -13294,7 +13298,7 @@
       <c r="H917" s="1"/>
       <c r="I917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" spans="8:8" ht="15.0">
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
       <c r="D918" s="1"/>
@@ -13304,7 +13308,7 @@
       <c r="H918" s="1"/>
       <c r="I918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" spans="8:8" ht="15.0">
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
       <c r="D919" s="1"/>
@@ -13314,7 +13318,7 @@
       <c r="H919" s="1"/>
       <c r="I919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" spans="8:8" ht="15.0">
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
       <c r="D920" s="1"/>
@@ -13324,7 +13328,7 @@
       <c r="H920" s="1"/>
       <c r="I920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" spans="8:8" ht="15.0">
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
       <c r="D921" s="1"/>
@@ -13334,7 +13338,7 @@
       <c r="H921" s="1"/>
       <c r="I921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" spans="8:8" ht="15.0">
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
       <c r="D922" s="1"/>
@@ -13344,7 +13348,7 @@
       <c r="H922" s="1"/>
       <c r="I922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" spans="8:8" ht="15.0">
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
       <c r="D923" s="1"/>
@@ -13354,7 +13358,7 @@
       <c r="H923" s="1"/>
       <c r="I923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" spans="8:8" ht="15.0">
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
       <c r="D924" s="1"/>
@@ -13364,7 +13368,7 @@
       <c r="H924" s="1"/>
       <c r="I924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" spans="8:8" ht="15.0">
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
       <c r="D925" s="1"/>
@@ -13374,7 +13378,7 @@
       <c r="H925" s="1"/>
       <c r="I925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" spans="8:8" ht="15.0">
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
       <c r="D926" s="1"/>
@@ -13384,7 +13388,7 @@
       <c r="H926" s="1"/>
       <c r="I926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" spans="8:8" ht="15.0">
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
       <c r="D927" s="1"/>
@@ -13394,7 +13398,7 @@
       <c r="H927" s="1"/>
       <c r="I927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" spans="8:8" ht="15.0">
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
       <c r="D928" s="1"/>
@@ -13404,7 +13408,7 @@
       <c r="H928" s="1"/>
       <c r="I928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" spans="8:8" ht="15.0">
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
       <c r="D929" s="1"/>
@@ -13414,7 +13418,7 @@
       <c r="H929" s="1"/>
       <c r="I929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" spans="8:8" ht="15.0">
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
       <c r="D930" s="1"/>
@@ -13424,7 +13428,7 @@
       <c r="H930" s="1"/>
       <c r="I930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" spans="8:8" ht="15.0">
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
       <c r="D931" s="1"/>
@@ -13434,7 +13438,7 @@
       <c r="H931" s="1"/>
       <c r="I931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" spans="8:8" ht="15.0">
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
       <c r="D932" s="1"/>
@@ -13444,7 +13448,7 @@
       <c r="H932" s="1"/>
       <c r="I932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" spans="8:8" ht="15.0">
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
       <c r="D933" s="1"/>
@@ -13454,7 +13458,7 @@
       <c r="H933" s="1"/>
       <c r="I933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" spans="8:8" ht="15.0">
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
       <c r="D934" s="1"/>
@@ -13464,7 +13468,7 @@
       <c r="H934" s="1"/>
       <c r="I934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" spans="8:8" ht="15.0">
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
       <c r="D935" s="1"/>
@@ -13474,7 +13478,7 @@
       <c r="H935" s="1"/>
       <c r="I935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" spans="8:8" ht="15.0">
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
       <c r="D936" s="1"/>
@@ -13484,7 +13488,7 @@
       <c r="H936" s="1"/>
       <c r="I936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" spans="8:8" ht="15.0">
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
       <c r="D937" s="1"/>
@@ -13494,7 +13498,7 @@
       <c r="H937" s="1"/>
       <c r="I937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" spans="8:8" ht="15.0">
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
       <c r="D938" s="1"/>
@@ -13504,7 +13508,7 @@
       <c r="H938" s="1"/>
       <c r="I938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" spans="8:8" ht="15.0">
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
       <c r="D939" s="1"/>
@@ -13514,7 +13518,7 @@
       <c r="H939" s="1"/>
       <c r="I939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" spans="8:8" ht="15.0">
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
       <c r="D940" s="1"/>
@@ -13524,7 +13528,7 @@
       <c r="H940" s="1"/>
       <c r="I940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" spans="8:8" ht="15.0">
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
       <c r="D941" s="1"/>
@@ -13534,7 +13538,7 @@
       <c r="H941" s="1"/>
       <c r="I941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" spans="8:8" ht="15.0">
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
       <c r="D942" s="1"/>
@@ -13544,7 +13548,7 @@
       <c r="H942" s="1"/>
       <c r="I942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" spans="8:8" ht="15.0">
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
       <c r="D943" s="1"/>
@@ -13554,7 +13558,7 @@
       <c r="H943" s="1"/>
       <c r="I943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" spans="8:8" ht="15.0">
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
       <c r="D944" s="1"/>
@@ -13564,7 +13568,7 @@
       <c r="H944" s="1"/>
       <c r="I944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" spans="8:8" ht="15.0">
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
       <c r="D945" s="1"/>
@@ -13574,7 +13578,7 @@
       <c r="H945" s="1"/>
       <c r="I945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" spans="8:8" ht="15.0">
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
       <c r="D946" s="1"/>
@@ -13584,7 +13588,7 @@
       <c r="H946" s="1"/>
       <c r="I946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" spans="8:8" ht="15.0">
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
       <c r="D947" s="1"/>
@@ -13594,7 +13598,7 @@
       <c r="H947" s="1"/>
       <c r="I947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" spans="8:8" ht="15.0">
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
       <c r="D948" s="1"/>
@@ -13604,7 +13608,7 @@
       <c r="H948" s="1"/>
       <c r="I948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" spans="8:8" ht="15.0">
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
       <c r="D949" s="1"/>
@@ -13614,7 +13618,7 @@
       <c r="H949" s="1"/>
       <c r="I949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" spans="8:8" ht="15.0">
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
       <c r="D950" s="1"/>
@@ -13624,7 +13628,7 @@
       <c r="H950" s="1"/>
       <c r="I950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" spans="8:8" ht="15.0">
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
       <c r="D951" s="1"/>
@@ -13634,7 +13638,7 @@
       <c r="H951" s="1"/>
       <c r="I951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" spans="8:8" ht="15.0">
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
       <c r="D952" s="1"/>
@@ -13644,7 +13648,7 @@
       <c r="H952" s="1"/>
       <c r="I952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" spans="8:8" ht="15.0">
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
       <c r="D953" s="1"/>
@@ -13654,7 +13658,7 @@
       <c r="H953" s="1"/>
       <c r="I953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" spans="8:8" ht="15.0">
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
       <c r="D954" s="1"/>
@@ -13664,7 +13668,7 @@
       <c r="H954" s="1"/>
       <c r="I954" s="3"/>
     </row>
-    <row r="955">
+    <row r="955" spans="8:8" ht="15.0">
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
       <c r="D955" s="1"/>
@@ -13674,7 +13678,7 @@
       <c r="H955" s="1"/>
       <c r="I955" s="3"/>
     </row>
-    <row r="956">
+    <row r="956" spans="8:8" ht="15.0">
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
       <c r="D956" s="1"/>
@@ -13684,7 +13688,7 @@
       <c r="H956" s="1"/>
       <c r="I956" s="3"/>
     </row>
-    <row r="957">
+    <row r="957" spans="8:8" ht="15.0">
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
       <c r="D957" s="1"/>
@@ -13694,7 +13698,7 @@
       <c r="H957" s="1"/>
       <c r="I957" s="3"/>
     </row>
-    <row r="958">
+    <row r="958" spans="8:8" ht="15.0">
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
       <c r="D958" s="1"/>
@@ -13704,7 +13708,7 @@
       <c r="H958" s="1"/>
       <c r="I958" s="3"/>
     </row>
-    <row r="959">
+    <row r="959" spans="8:8" ht="15.0">
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
       <c r="D959" s="1"/>
@@ -13714,7 +13718,7 @@
       <c r="H959" s="1"/>
       <c r="I959" s="3"/>
     </row>
-    <row r="960">
+    <row r="960" spans="8:8" ht="15.0">
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
       <c r="D960" s="1"/>
@@ -13724,7 +13728,7 @@
       <c r="H960" s="1"/>
       <c r="I960" s="3"/>
     </row>
-    <row r="961">
+    <row r="961" spans="8:8" ht="15.0">
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
       <c r="D961" s="1"/>
@@ -13734,7 +13738,7 @@
       <c r="H961" s="1"/>
       <c r="I961" s="3"/>
     </row>
-    <row r="962">
+    <row r="962" spans="8:8" ht="15.0">
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
       <c r="D962" s="1"/>
@@ -13744,7 +13748,7 @@
       <c r="H962" s="1"/>
       <c r="I962" s="3"/>
     </row>
-    <row r="963">
+    <row r="963" spans="8:8" ht="15.0">
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
       <c r="D963" s="1"/>
@@ -13754,7 +13758,7 @@
       <c r="H963" s="1"/>
       <c r="I963" s="3"/>
     </row>
-    <row r="964">
+    <row r="964" spans="8:8" ht="15.0">
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
       <c r="D964" s="1"/>
@@ -13764,7 +13768,7 @@
       <c r="H964" s="1"/>
       <c r="I964" s="3"/>
     </row>
-    <row r="965">
+    <row r="965" spans="8:8" ht="15.0">
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
       <c r="D965" s="1"/>
@@ -13774,7 +13778,7 @@
       <c r="H965" s="1"/>
       <c r="I965" s="3"/>
     </row>
-    <row r="966">
+    <row r="966" spans="8:8" ht="15.0">
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
       <c r="D966" s="1"/>
@@ -13784,7 +13788,7 @@
       <c r="H966" s="1"/>
       <c r="I966" s="3"/>
     </row>
-    <row r="967">
+    <row r="967" spans="8:8" ht="15.0">
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
       <c r="D967" s="1"/>
@@ -13794,7 +13798,7 @@
       <c r="H967" s="1"/>
       <c r="I967" s="3"/>
     </row>
-    <row r="968">
+    <row r="968" spans="8:8" ht="15.0">
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
       <c r="D968" s="1"/>
@@ -13804,7 +13808,7 @@
       <c r="H968" s="1"/>
       <c r="I968" s="3"/>
     </row>
-    <row r="969">
+    <row r="969" spans="8:8" ht="15.0">
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
       <c r="D969" s="1"/>
@@ -13814,7 +13818,7 @@
       <c r="H969" s="1"/>
       <c r="I969" s="3"/>
     </row>
-    <row r="970">
+    <row r="970" spans="8:8" ht="15.0">
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
       <c r="D970" s="1"/>
@@ -13824,7 +13828,7 @@
       <c r="H970" s="1"/>
       <c r="I970" s="3"/>
     </row>
-    <row r="971">
+    <row r="971" spans="8:8" ht="15.0">
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
       <c r="D971" s="1"/>
@@ -13834,7 +13838,7 @@
       <c r="H971" s="1"/>
       <c r="I971" s="3"/>
     </row>
-    <row r="972">
+    <row r="972" spans="8:8" ht="15.0">
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
       <c r="D972" s="1"/>
@@ -13844,7 +13848,7 @@
       <c r="H972" s="1"/>
       <c r="I972" s="3"/>
     </row>
-    <row r="973">
+    <row r="973" spans="8:8" ht="15.0">
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
       <c r="D973" s="1"/>
@@ -13854,7 +13858,7 @@
       <c r="H973" s="1"/>
       <c r="I973" s="3"/>
     </row>
-    <row r="974">
+    <row r="974" spans="8:8" ht="15.0">
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
       <c r="D974" s="1"/>
@@ -13864,7 +13868,7 @@
       <c r="H974" s="1"/>
       <c r="I974" s="3"/>
     </row>
-    <row r="975">
+    <row r="975" spans="8:8" ht="15.0">
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
       <c r="D975" s="1"/>
@@ -13874,7 +13878,7 @@
       <c r="H975" s="1"/>
       <c r="I975" s="3"/>
     </row>
-    <row r="976">
+    <row r="976" spans="8:8" ht="15.0">
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
       <c r="D976" s="1"/>
@@ -13884,7 +13888,7 @@
       <c r="H976" s="1"/>
       <c r="I976" s="3"/>
     </row>
-    <row r="977">
+    <row r="977" spans="8:8" ht="15.0">
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
       <c r="D977" s="1"/>
@@ -13894,7 +13898,7 @@
       <c r="H977" s="1"/>
       <c r="I977" s="3"/>
     </row>
-    <row r="978">
+    <row r="978" spans="8:8" ht="15.0">
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
       <c r="D978" s="1"/>
@@ -13904,7 +13908,7 @@
       <c r="H978" s="1"/>
       <c r="I978" s="3"/>
     </row>
-    <row r="979">
+    <row r="979" spans="8:8" ht="15.0">
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
       <c r="D979" s="1"/>
@@ -13914,7 +13918,7 @@
       <c r="H979" s="1"/>
       <c r="I979" s="3"/>
     </row>
-    <row r="980">
+    <row r="980" spans="8:8" ht="15.0">
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
       <c r="D980" s="1"/>
@@ -13924,7 +13928,7 @@
       <c r="H980" s="1"/>
       <c r="I980" s="3"/>
     </row>
-    <row r="981">
+    <row r="981" spans="8:8" ht="15.0">
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
       <c r="D981" s="1"/>
@@ -13934,7 +13938,7 @@
       <c r="H981" s="1"/>
       <c r="I981" s="3"/>
     </row>
-    <row r="982">
+    <row r="982" spans="8:8" ht="15.0">
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
       <c r="D982" s="1"/>
@@ -13944,7 +13948,7 @@
       <c r="H982" s="1"/>
       <c r="I982" s="3"/>
     </row>
-    <row r="983">
+    <row r="983" spans="8:8" ht="15.0">
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
       <c r="D983" s="1"/>
@@ -13954,7 +13958,7 @@
       <c r="H983" s="1"/>
       <c r="I983" s="3"/>
     </row>
-    <row r="984">
+    <row r="984" spans="8:8" ht="15.0">
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
       <c r="D984" s="1"/>
@@ -13964,7 +13968,7 @@
       <c r="H984" s="1"/>
       <c r="I984" s="3"/>
     </row>
-    <row r="985">
+    <row r="985" spans="8:8" ht="15.0">
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
       <c r="D985" s="1"/>
@@ -13974,7 +13978,7 @@
       <c r="H985" s="1"/>
       <c r="I985" s="3"/>
     </row>
-    <row r="986">
+    <row r="986" spans="8:8" ht="15.0">
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
       <c r="D986" s="1"/>
@@ -13984,7 +13988,7 @@
       <c r="H986" s="1"/>
       <c r="I986" s="3"/>
     </row>
-    <row r="987">
+    <row r="987" spans="8:8" ht="15.0">
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
       <c r="D987" s="1"/>
@@ -13994,7 +13998,7 @@
       <c r="H987" s="1"/>
       <c r="I987" s="3"/>
     </row>
-    <row r="988">
+    <row r="988" spans="8:8" ht="15.0">
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
       <c r="D988" s="1"/>
@@ -14004,7 +14008,7 @@
       <c r="H988" s="1"/>
       <c r="I988" s="3"/>
     </row>
-    <row r="989">
+    <row r="989" spans="8:8" ht="15.0">
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
       <c r="D989" s="1"/>
@@ -14014,7 +14018,7 @@
       <c r="H989" s="1"/>
       <c r="I989" s="3"/>
     </row>
-    <row r="990">
+    <row r="990" spans="8:8" ht="15.0">
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
       <c r="D990" s="1"/>
@@ -14024,7 +14028,7 @@
       <c r="H990" s="1"/>
       <c r="I990" s="3"/>
     </row>
-    <row r="991">
+    <row r="991" spans="8:8" ht="15.0">
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
       <c r="D991" s="1"/>
@@ -14034,7 +14038,7 @@
       <c r="H991" s="1"/>
       <c r="I991" s="3"/>
     </row>
-    <row r="992">
+    <row r="992" spans="8:8" ht="15.0">
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
       <c r="D992" s="1"/>
@@ -14044,7 +14048,7 @@
       <c r="H992" s="1"/>
       <c r="I992" s="3"/>
     </row>
-    <row r="993">
+    <row r="993" spans="8:8" ht="15.0">
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
       <c r="D993" s="1"/>
@@ -14054,7 +14058,7 @@
       <c r="H993" s="1"/>
       <c r="I993" s="3"/>
     </row>
-    <row r="994">
+    <row r="994" spans="8:8" ht="15.0">
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
       <c r="D994" s="1"/>
@@ -14064,7 +14068,7 @@
       <c r="H994" s="1"/>
       <c r="I994" s="3"/>
     </row>
-    <row r="995">
+    <row r="995" spans="8:8" ht="15.0">
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
       <c r="D995" s="1"/>
@@ -14074,7 +14078,7 @@
       <c r="H995" s="1"/>
       <c r="I995" s="3"/>
     </row>
-    <row r="996">
+    <row r="996" spans="8:8" ht="15.0">
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
       <c r="D996" s="1"/>
@@ -14084,7 +14088,7 @@
       <c r="H996" s="1"/>
       <c r="I996" s="3"/>
     </row>
-    <row r="997">
+    <row r="997" spans="8:8" ht="15.0">
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
       <c r="D997" s="1"/>
@@ -14094,7 +14098,7 @@
       <c r="H997" s="1"/>
       <c r="I997" s="3"/>
     </row>
-    <row r="998">
+    <row r="998" spans="8:8" ht="15.0">
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
       <c r="D998" s="1"/>
@@ -14104,7 +14108,7 @@
       <c r="H998" s="1"/>
       <c r="I998" s="3"/>
     </row>
-    <row r="999">
+    <row r="999" spans="8:8" ht="15.0">
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
       <c r="D999" s="1"/>
@@ -14114,7 +14118,7 @@
       <c r="H999" s="1"/>
       <c r="I999" s="3"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="8:8" ht="15.0">
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
       <c r="D1000" s="1"/>
@@ -14125,6 +14129,6 @@
       <c r="I1000" s="3"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>